--- a/data/nzd0012/nzd0012.xlsx
+++ b/data/nzd0012/nzd0012.xlsx
@@ -18546,7 +18546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B204"/>
+  <dimension ref="A1:B205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20589,6 +20589,16 @@
       </c>
       <c r="B204" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0012/nzd0012.xlsx
+++ b/data/nzd0012/nzd0012.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB203"/>
+  <dimension ref="A1:AB204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18535,6 +18535,96 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>340.54</v>
+      </c>
+      <c r="C204" t="n">
+        <v>346.76</v>
+      </c>
+      <c r="D204" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="E204" t="n">
+        <v>339.88</v>
+      </c>
+      <c r="F204" t="n">
+        <v>333.81</v>
+      </c>
+      <c r="G204" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="H204" t="n">
+        <v>348.87</v>
+      </c>
+      <c r="I204" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="J204" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="K204" t="n">
+        <v>363.86</v>
+      </c>
+      <c r="L204" t="n">
+        <v>364.67</v>
+      </c>
+      <c r="M204" t="n">
+        <v>363.28</v>
+      </c>
+      <c r="N204" t="n">
+        <v>360.67</v>
+      </c>
+      <c r="O204" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="P204" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>367.28</v>
+      </c>
+      <c r="R204" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="S204" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="T204" t="n">
+        <v>369.62</v>
+      </c>
+      <c r="U204" t="n">
+        <v>367.89</v>
+      </c>
+      <c r="V204" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="W204" t="n">
+        <v>363.69</v>
+      </c>
+      <c r="X204" t="n">
+        <v>372.38</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>375.24</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>374.52</v>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18546,7 +18636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B205"/>
+  <dimension ref="A1:B206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20599,6 +20689,16 @@
       </c>
       <c r="B205" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -20767,28 +20867,28 @@
         <v>0.0363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1321754409204459</v>
+        <v>0.111187587293454</v>
       </c>
       <c r="J2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005370644863745722</v>
+        <v>0.003807711263380975</v>
       </c>
       <c r="M2" t="n">
-        <v>10.93315165676894</v>
+        <v>10.98251852742047</v>
       </c>
       <c r="N2" t="n">
-        <v>203.4053912263218</v>
+        <v>204.7300254501155</v>
       </c>
       <c r="O2" t="n">
-        <v>14.26202619638324</v>
+        <v>14.30839003697186</v>
       </c>
       <c r="P2" t="n">
-        <v>358.8730810593501</v>
+        <v>359.0623735018569</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20845,28 +20945,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1536268165533925</v>
+        <v>0.1356354742379294</v>
       </c>
       <c r="J3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01034934082765049</v>
+        <v>0.008082656217447637</v>
       </c>
       <c r="M3" t="n">
-        <v>9.065367950596267</v>
+        <v>9.125608243594693</v>
       </c>
       <c r="N3" t="n">
-        <v>143.4236135265961</v>
+        <v>144.4568602989224</v>
       </c>
       <c r="O3" t="n">
-        <v>11.97595981650724</v>
+        <v>12.01902077121603</v>
       </c>
       <c r="P3" t="n">
-        <v>361.5984915635393</v>
+        <v>361.7590180346353</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20923,28 +21023,28 @@
         <v>0.0382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1536427109714645</v>
+        <v>0.1401840427464415</v>
       </c>
       <c r="J4" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K4" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01272822361568715</v>
+        <v>0.01065507978874702</v>
       </c>
       <c r="M4" t="n">
-        <v>7.724252744079362</v>
+        <v>7.766537050935332</v>
       </c>
       <c r="N4" t="n">
-        <v>115.1115587849143</v>
+        <v>115.4989253595677</v>
       </c>
       <c r="O4" t="n">
-        <v>10.72900548908958</v>
+        <v>10.74704263318834</v>
       </c>
       <c r="P4" t="n">
-        <v>363.272327514971</v>
+        <v>363.3937131614732</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21001,28 +21101,28 @@
         <v>0.0403</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1636394010668504</v>
+        <v>0.1428028854175791</v>
       </c>
       <c r="J5" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00848554594804185</v>
+        <v>0.006475996162777387</v>
       </c>
       <c r="M5" t="n">
-        <v>10.36528703935267</v>
+        <v>10.41329187178474</v>
       </c>
       <c r="N5" t="n">
-        <v>196.7075863082657</v>
+        <v>198.0320610860276</v>
       </c>
       <c r="O5" t="n">
-        <v>14.02524817278702</v>
+        <v>14.07238647444091</v>
       </c>
       <c r="P5" t="n">
-        <v>357.2277887543425</v>
+        <v>357.4157162580635</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21079,28 +21179,28 @@
         <v>0.0402</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3197339868711765</v>
+        <v>0.2924124773045834</v>
       </c>
       <c r="J6" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02523899843751154</v>
+        <v>0.02111247037345965</v>
       </c>
       <c r="M6" t="n">
-        <v>11.90777151818342</v>
+        <v>11.97066056134434</v>
       </c>
       <c r="N6" t="n">
-        <v>248.2159708094311</v>
+        <v>250.9431259752476</v>
       </c>
       <c r="O6" t="n">
-        <v>15.75487133585772</v>
+        <v>15.84118448775999</v>
       </c>
       <c r="P6" t="n">
-        <v>353.7813780993452</v>
+        <v>354.0277946872799</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21157,28 +21257,28 @@
         <v>0.0688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1424930587739233</v>
+        <v>0.1273235306561725</v>
       </c>
       <c r="J7" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K7" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005789385218352594</v>
+        <v>0.004656596037143412</v>
       </c>
       <c r="M7" t="n">
-        <v>11.22712946334853</v>
+        <v>11.24591611073345</v>
       </c>
       <c r="N7" t="n">
-        <v>219.2095410261873</v>
+        <v>219.3367909824003</v>
       </c>
       <c r="O7" t="n">
-        <v>14.80572662945616</v>
+        <v>14.81002332821932</v>
       </c>
       <c r="P7" t="n">
-        <v>357.8106245786065</v>
+        <v>357.9474407142686</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21235,28 +21335,28 @@
         <v>0.0762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1382301071057473</v>
+        <v>0.1235682047616056</v>
       </c>
       <c r="J8" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K8" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006532362490255794</v>
+        <v>0.005255994214390936</v>
       </c>
       <c r="M8" t="n">
-        <v>10.39701572021907</v>
+        <v>10.41437270083427</v>
       </c>
       <c r="N8" t="n">
-        <v>182.6900201929366</v>
+        <v>182.9193659245888</v>
       </c>
       <c r="O8" t="n">
-        <v>13.516287219238</v>
+        <v>13.52476860891116</v>
       </c>
       <c r="P8" t="n">
-        <v>360.4677850706612</v>
+        <v>360.6000228571374</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21313,28 +21413,28 @@
         <v>0.0827</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1757468616684078</v>
+        <v>0.1614703507717867</v>
       </c>
       <c r="J9" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008943607105128537</v>
+        <v>0.007612597026474988</v>
       </c>
       <c r="M9" t="n">
-        <v>10.91031478822728</v>
+        <v>10.90945096421866</v>
       </c>
       <c r="N9" t="n">
-        <v>215.2693646428615</v>
+        <v>215.2600866236819</v>
       </c>
       <c r="O9" t="n">
-        <v>14.67206068154237</v>
+        <v>14.67174449830973</v>
       </c>
       <c r="P9" t="n">
-        <v>362.9727600234174</v>
+        <v>363.1011725813593</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21391,28 +21491,28 @@
         <v>0.0687</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2195477856203839</v>
+        <v>0.2046933348645807</v>
       </c>
       <c r="J10" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01651917457711793</v>
+        <v>0.01446776961897189</v>
       </c>
       <c r="M10" t="n">
-        <v>10.16722222144618</v>
+        <v>10.17756656743161</v>
       </c>
       <c r="N10" t="n">
-        <v>181.5395324477629</v>
+        <v>181.8097953234514</v>
       </c>
       <c r="O10" t="n">
-        <v>13.47366069217133</v>
+        <v>13.48368626613106</v>
       </c>
       <c r="P10" t="n">
-        <v>367.1585939041209</v>
+        <v>367.2911790902013</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21469,28 +21569,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1439404524730004</v>
+        <v>0.1342988843300503</v>
       </c>
       <c r="J11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K11" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007026085442749186</v>
+        <v>0.006182352454961459</v>
       </c>
       <c r="M11" t="n">
-        <v>10.13371923222702</v>
+        <v>10.11775279241102</v>
       </c>
       <c r="N11" t="n">
-        <v>181.1710302211606</v>
+        <v>180.7186576930036</v>
       </c>
       <c r="O11" t="n">
-        <v>13.45997883435039</v>
+        <v>13.44316397627447</v>
       </c>
       <c r="P11" t="n">
-        <v>369.7200132430845</v>
+        <v>369.8068929498316</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21547,28 +21647,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1454727721744328</v>
+        <v>0.1354389549569047</v>
       </c>
       <c r="J12" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K12" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007526405424666094</v>
+        <v>0.006588684824362145</v>
       </c>
       <c r="M12" t="n">
-        <v>10.06507856225516</v>
+        <v>10.05616179582665</v>
       </c>
       <c r="N12" t="n">
-        <v>174.6391933929295</v>
+        <v>174.2933896852168</v>
       </c>
       <c r="O12" t="n">
-        <v>13.21511231102216</v>
+        <v>13.20202218166659</v>
       </c>
       <c r="P12" t="n">
-        <v>371.1883420379187</v>
+        <v>371.2788680653341</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21625,28 +21725,28 @@
         <v>0.0911</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1410445259031552</v>
+        <v>0.1308870978908298</v>
       </c>
       <c r="J13" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K13" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008183768729438046</v>
+        <v>0.007114824755186877</v>
       </c>
       <c r="M13" t="n">
-        <v>9.369628582080276</v>
+        <v>9.360993110915446</v>
       </c>
       <c r="N13" t="n">
-        <v>149.248475732872</v>
+        <v>149.030793801646</v>
       </c>
       <c r="O13" t="n">
-        <v>12.21672933861072</v>
+        <v>12.20781691383214</v>
       </c>
       <c r="P13" t="n">
-        <v>369.9417517850565</v>
+        <v>370.0343748131307</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21703,28 +21803,28 @@
         <v>0.0549</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2369607107829285</v>
+        <v>0.2244133172318653</v>
       </c>
       <c r="J14" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K14" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01438278455736297</v>
+        <v>0.01303219522774945</v>
       </c>
       <c r="M14" t="n">
-        <v>12.07058603787966</v>
+        <v>12.04965149101685</v>
       </c>
       <c r="N14" t="n">
-        <v>237.8070492966907</v>
+        <v>237.3982646036485</v>
       </c>
       <c r="O14" t="n">
-        <v>15.42099378434123</v>
+        <v>15.40773392175658</v>
       </c>
       <c r="P14" t="n">
-        <v>367.0697950773292</v>
+        <v>367.1841347381252</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -21781,28 +21881,28 @@
         <v>0.0408</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3493127061577375</v>
+        <v>0.3301999695423933</v>
       </c>
       <c r="J15" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K15" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01527486399292111</v>
+        <v>0.01379416591309446</v>
       </c>
       <c r="M15" t="n">
-        <v>17.22978006303005</v>
+        <v>17.19913475042694</v>
       </c>
       <c r="N15" t="n">
-        <v>475.7031338959696</v>
+        <v>474.9749511475541</v>
       </c>
       <c r="O15" t="n">
-        <v>21.81061975038696</v>
+        <v>21.79392005004043</v>
       </c>
       <c r="P15" t="n">
-        <v>362.0129811939725</v>
+        <v>362.18915486159</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -21859,28 +21959,28 @@
         <v>0.046</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3667003835786964</v>
+        <v>0.356627735374862</v>
       </c>
       <c r="J16" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K16" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01916478163673296</v>
+        <v>0.01833718710508325</v>
       </c>
       <c r="M16" t="n">
-        <v>16.39757975966673</v>
+        <v>16.3607393480393</v>
       </c>
       <c r="N16" t="n">
-        <v>430.6870757087221</v>
+        <v>429.0651225162142</v>
       </c>
       <c r="O16" t="n">
-        <v>20.75300160720666</v>
+        <v>20.7138871899075</v>
       </c>
       <c r="P16" t="n">
-        <v>364.1495926418386</v>
+        <v>364.2404690060058</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -21937,28 +22037,28 @@
         <v>0.0605</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4028979238966484</v>
+        <v>0.3906481322145361</v>
       </c>
       <c r="J17" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K17" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03132951874648782</v>
+        <v>0.02978046574786386</v>
       </c>
       <c r="M17" t="n">
-        <v>13.54403910175063</v>
+        <v>13.52164133676036</v>
       </c>
       <c r="N17" t="n">
-        <v>314.0937795421193</v>
+        <v>313.3093762369869</v>
       </c>
       <c r="O17" t="n">
-        <v>17.7226910919905</v>
+        <v>17.70054734286448</v>
       </c>
       <c r="P17" t="n">
-        <v>369.2916740253177</v>
+        <v>369.4021927794075</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22015,28 +22115,28 @@
         <v>0.0604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4157919164120845</v>
+        <v>0.4068424878525669</v>
       </c>
       <c r="J18" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K18" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04442916016918264</v>
+        <v>0.04303622556024533</v>
       </c>
       <c r="M18" t="n">
-        <v>12.23241234012672</v>
+        <v>12.20803881368245</v>
       </c>
       <c r="N18" t="n">
-        <v>230.1793917661588</v>
+        <v>229.4359378092897</v>
       </c>
       <c r="O18" t="n">
-        <v>15.17166410668779</v>
+        <v>15.14714289261475</v>
       </c>
       <c r="P18" t="n">
-        <v>372.5143685714584</v>
+        <v>372.595976156736</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22093,28 +22193,28 @@
         <v>0.0539</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2592396155298594</v>
+        <v>0.2503477663491825</v>
       </c>
       <c r="J19" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K19" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01926317180833159</v>
+        <v>0.01816553535438359</v>
       </c>
       <c r="M19" t="n">
-        <v>11.19360741089639</v>
+        <v>11.17674350327971</v>
       </c>
       <c r="N19" t="n">
-        <v>214.1284424745352</v>
+        <v>213.4719768596688</v>
       </c>
       <c r="O19" t="n">
-        <v>14.63312825319778</v>
+        <v>14.61068023261302</v>
       </c>
       <c r="P19" t="n">
-        <v>374.5143674733526</v>
+        <v>374.5945905594676</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -22171,28 +22271,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4211304510466822</v>
+        <v>0.4104003362768867</v>
       </c>
       <c r="J20" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K20" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0553364455780998</v>
+        <v>0.05317144881324676</v>
       </c>
       <c r="M20" t="n">
-        <v>10.93216389554119</v>
+        <v>10.91691959804841</v>
       </c>
       <c r="N20" t="n">
-        <v>186.1070341048038</v>
+        <v>185.725196112007</v>
       </c>
       <c r="O20" t="n">
-        <v>13.64210519329051</v>
+        <v>13.62810317366313</v>
       </c>
       <c r="P20" t="n">
-        <v>369.1441750986592</v>
+        <v>369.2417624563565</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -22249,28 +22349,28 @@
         <v>0.0654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1502399305280354</v>
+        <v>0.1390539435733331</v>
       </c>
       <c r="J21" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K21" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L21" t="n">
-        <v>0.008252402315518048</v>
+        <v>0.007133569595250688</v>
       </c>
       <c r="M21" t="n">
-        <v>10.01685278610586</v>
+        <v>10.0074259798865</v>
       </c>
       <c r="N21" t="n">
-        <v>173.384255166751</v>
+        <v>173.1848733497358</v>
       </c>
       <c r="O21" t="n">
-        <v>13.16754552552415</v>
+        <v>13.15997239167833</v>
       </c>
       <c r="P21" t="n">
-        <v>375.5972305571685</v>
+        <v>375.6969053098443</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -22327,28 +22427,28 @@
         <v>0.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>0.21296444350342</v>
+        <v>0.2021910364123111</v>
       </c>
       <c r="J22" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K22" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01677153390519082</v>
+        <v>0.01526183882958321</v>
       </c>
       <c r="M22" t="n">
-        <v>10.08540781428959</v>
+        <v>10.06166001467173</v>
       </c>
       <c r="N22" t="n">
-        <v>169.006369439841</v>
+        <v>168.7920765786731</v>
       </c>
       <c r="O22" t="n">
-        <v>13.00024497614722</v>
+        <v>12.99200048409301</v>
       </c>
       <c r="P22" t="n">
-        <v>371.8275921287391</v>
+        <v>371.9241506141183</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -22405,28 +22505,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01240744437671277</v>
+        <v>0.00125559748416028</v>
       </c>
       <c r="J23" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K23" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L23" t="n">
-        <v>6.216309346673832e-05</v>
+        <v>6.413669355609386e-07</v>
       </c>
       <c r="M23" t="n">
-        <v>9.399059963988648</v>
+        <v>9.383487195487433</v>
       </c>
       <c r="N23" t="n">
-        <v>156.2382141297859</v>
+        <v>156.1202151710523</v>
       </c>
       <c r="O23" t="n">
-        <v>12.49952855630107</v>
+        <v>12.49480752837163</v>
       </c>
       <c r="P23" t="n">
-        <v>374.9841791702468</v>
+        <v>375.0852572077624</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -22483,28 +22583,28 @@
         <v>0.0519</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02750814628409541</v>
+        <v>0.01968808494437542</v>
       </c>
       <c r="J24" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K24" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0004043871566786761</v>
+        <v>0.0002090463827583156</v>
       </c>
       <c r="M24" t="n">
-        <v>8.552415296709372</v>
+        <v>8.535473993829577</v>
       </c>
       <c r="N24" t="n">
-        <v>117.5760366846975</v>
+        <v>117.3132991053016</v>
       </c>
       <c r="O24" t="n">
-        <v>10.84324843783898</v>
+        <v>10.83112640057818</v>
       </c>
       <c r="P24" t="n">
-        <v>379.7972935627692</v>
+        <v>379.8682308517377</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -22561,28 +22661,28 @@
         <v>0.0529</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1264307202355788</v>
+        <v>-0.1345782736307594</v>
       </c>
       <c r="J25" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K25" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L25" t="n">
-        <v>0.006287174935071693</v>
+        <v>0.007184879378071551</v>
       </c>
       <c r="M25" t="n">
-        <v>10.21827197299898</v>
+        <v>10.19194000631694</v>
       </c>
       <c r="N25" t="n">
-        <v>159.5539552687972</v>
+        <v>159.0978674230492</v>
       </c>
       <c r="O25" t="n">
-        <v>12.63146686924354</v>
+        <v>12.61340031169427</v>
       </c>
       <c r="P25" t="n">
-        <v>392.3488771377204</v>
+        <v>392.4228971648914</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -22639,28 +22739,28 @@
         <v>0.042</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.07547288762159969</v>
+        <v>-0.08345383694864517</v>
       </c>
       <c r="J26" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K26" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001488713207842607</v>
+        <v>0.001838625009752737</v>
       </c>
       <c r="M26" t="n">
-        <v>12.69972270613934</v>
+        <v>12.6692378722149</v>
       </c>
       <c r="N26" t="n">
-        <v>235.5678670916306</v>
+        <v>234.7103265090986</v>
       </c>
       <c r="O26" t="n">
-        <v>15.34822032326975</v>
+        <v>15.32025869589344</v>
       </c>
       <c r="P26" t="n">
-        <v>385.4134193073741</v>
+        <v>385.4870305476865</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -22721,28 +22821,28 @@
         <v>0.0332</v>
       </c>
       <c r="I27" t="n">
-        <v>0.02038075699900502</v>
+        <v>0.0124623047841023</v>
       </c>
       <c r="J27" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K27" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0001064990770700547</v>
+        <v>4.024155937809581e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>12.76732964768096</v>
+        <v>12.73168683032917</v>
       </c>
       <c r="N27" t="n">
-        <v>245.5011905330506</v>
+        <v>244.5889403773054</v>
       </c>
       <c r="O27" t="n">
-        <v>15.66847760738262</v>
+        <v>15.63933951218226</v>
       </c>
       <c r="P27" t="n">
-        <v>382.159471315633</v>
+        <v>382.2312353656434</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -22784,7 +22884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB203"/>
+  <dimension ref="A1:AB204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51177,6 +51277,148 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>-34.71055446312688,173.0700109171988</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>-34.71107479625544,173.07065177892824</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>-34.71159305455407,173.07129552554247</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-34.7122297555528,173.07177427368947</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-34.712822790063626,173.072313844978</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-34.713309119781016,173.07300243181817</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-34.71384748913271,173.07361973085747</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-34.71437464833217,173.07425144627362</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-34.71489779305556,173.07488727059953</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-34.7154101244557,173.07553776023428</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-34.71595587906056,173.07614280413188</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>-34.71650349209138,173.07674503454817</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-34.7170277678618,173.07737873480198</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>-34.71758673164316,173.0779723097866</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>-34.718023945545525,173.0787052970748</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>-34.7185058446382,173.07938711157232</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>-34.71896403688217,173.08008986757616</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>-34.71943863846302,173.08077185605168</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>-34.71991486266069,173.08145859601092</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>-34.72038440885609,173.08215005798505</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>-34.72080774773973,173.08288197362913</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>-34.72121195639595,173.0836336702943</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>-34.72153097774116,173.08444918759483</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>-34.72184675341761,173.0852471547049</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>-34.72214401274898,173.08604331002695</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>-34.72236874873168,173.08689521287292</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0012/nzd0012.xlsx
+++ b/data/nzd0012/nzd0012.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB204"/>
+  <dimension ref="A1:AB205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18554,7 +18554,7 @@
         <v>339.88</v>
       </c>
       <c r="F204" t="n">
-        <v>333.81</v>
+        <v>339.15</v>
       </c>
       <c r="G204" t="n">
         <v>345.8</v>
@@ -18620,6 +18620,96 @@
         <v>374.52</v>
       </c>
       <c r="AB204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>369.31</v>
+      </c>
+      <c r="C205" t="n">
+        <v>365.56</v>
+      </c>
+      <c r="D205" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="E205" t="n">
+        <v>366.87</v>
+      </c>
+      <c r="F205" t="n">
+        <v>369.33</v>
+      </c>
+      <c r="G205" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="H205" t="n">
+        <v>364.73</v>
+      </c>
+      <c r="I205" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="J205" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="L205" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="M205" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="N205" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="O205" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="P205" t="n">
+        <v>376.33</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="R205" t="n">
+        <v>384.68</v>
+      </c>
+      <c r="S205" t="n">
+        <v>380.23</v>
+      </c>
+      <c r="T205" t="n">
+        <v>377.16</v>
+      </c>
+      <c r="U205" t="n">
+        <v>381.63</v>
+      </c>
+      <c r="V205" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="W205" t="n">
+        <v>374.85</v>
+      </c>
+      <c r="X205" t="n">
+        <v>382</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>394.29</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>387.77</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="AB205" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18636,7 +18726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B206"/>
+  <dimension ref="A1:B207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20699,6 +20789,16 @@
       </c>
       <c r="B206" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -20867,28 +20967,28 @@
         <v>0.0363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.111187587293454</v>
+        <v>0.1181638229119615</v>
       </c>
       <c r="J2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003807711263380975</v>
+        <v>0.004343803983496652</v>
       </c>
       <c r="M2" t="n">
-        <v>10.98251852742047</v>
+        <v>10.96523969664861</v>
       </c>
       <c r="N2" t="n">
-        <v>204.7300254501155</v>
+        <v>203.9720599817977</v>
       </c>
       <c r="O2" t="n">
-        <v>14.30839003697186</v>
+        <v>14.28187872731727</v>
       </c>
       <c r="P2" t="n">
-        <v>359.0623735018569</v>
+        <v>358.9990664963053</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20945,28 +21045,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1356354742379294</v>
+        <v>0.1358279170132083</v>
       </c>
       <c r="J3" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008082656217447637</v>
+        <v>0.00820068735724333</v>
       </c>
       <c r="M3" t="n">
-        <v>9.125608243594693</v>
+        <v>9.081295513265157</v>
       </c>
       <c r="N3" t="n">
-        <v>144.4568602989224</v>
+        <v>143.7419286292775</v>
       </c>
       <c r="O3" t="n">
-        <v>12.01902077121603</v>
+        <v>11.98924220412939</v>
       </c>
       <c r="P3" t="n">
-        <v>361.7590180346353</v>
+        <v>361.7572903006384</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21023,28 +21123,28 @@
         <v>0.0382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1401840427464415</v>
+        <v>0.141568118554382</v>
       </c>
       <c r="J4" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01065507978874702</v>
+        <v>0.01099114388140154</v>
       </c>
       <c r="M4" t="n">
-        <v>7.766537050935332</v>
+        <v>7.73369853495586</v>
       </c>
       <c r="N4" t="n">
-        <v>115.4989253595677</v>
+        <v>114.9345612651518</v>
       </c>
       <c r="O4" t="n">
-        <v>10.74704263318834</v>
+        <v>10.72075376385223</v>
       </c>
       <c r="P4" t="n">
-        <v>363.3937131614732</v>
+        <v>363.3811531363179</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21101,28 +21201,28 @@
         <v>0.0403</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1428028854175791</v>
+        <v>0.1482144726059892</v>
       </c>
       <c r="J5" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K5" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006475996162777387</v>
+        <v>0.007049468227598887</v>
       </c>
       <c r="M5" t="n">
-        <v>10.41329187178474</v>
+        <v>10.39133384370178</v>
       </c>
       <c r="N5" t="n">
-        <v>198.0320610860276</v>
+        <v>197.2036348392912</v>
       </c>
       <c r="O5" t="n">
-        <v>14.07238647444091</v>
+        <v>14.04292116474671</v>
       </c>
       <c r="P5" t="n">
-        <v>357.4157162580635</v>
+        <v>357.366607913834</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21179,28 +21279,28 @@
         <v>0.0402</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2924124773045834</v>
+        <v>0.3046725408499127</v>
       </c>
       <c r="J6" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K6" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02111247037345965</v>
+        <v>0.02324225899676713</v>
       </c>
       <c r="M6" t="n">
-        <v>11.97066056134434</v>
+        <v>11.92918720371402</v>
       </c>
       <c r="N6" t="n">
-        <v>250.9431259752476</v>
+        <v>248.6208738546381</v>
       </c>
       <c r="O6" t="n">
-        <v>15.84118448775999</v>
+        <v>15.76771619019819</v>
       </c>
       <c r="P6" t="n">
-        <v>354.0277946872799</v>
+        <v>353.9168239765391</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21257,28 +21357,28 @@
         <v>0.0688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1273235306561725</v>
+        <v>0.1310278286295921</v>
       </c>
       <c r="J7" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K7" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004656596037143412</v>
+        <v>0.004986854927669371</v>
       </c>
       <c r="M7" t="n">
-        <v>11.24591611073345</v>
+        <v>11.2098577651525</v>
       </c>
       <c r="N7" t="n">
-        <v>219.3367909824003</v>
+        <v>218.3190366133107</v>
       </c>
       <c r="O7" t="n">
-        <v>14.81002332821932</v>
+        <v>14.77562305330339</v>
       </c>
       <c r="P7" t="n">
-        <v>357.9474407142686</v>
+        <v>357.9138254487884</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21335,28 +21435,28 @@
         <v>0.0762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1235682047616056</v>
+        <v>0.1243829887503318</v>
       </c>
       <c r="J8" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K8" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005255994214390936</v>
+        <v>0.005388103785957221</v>
       </c>
       <c r="M8" t="n">
-        <v>10.41437270083427</v>
+        <v>10.36710598651931</v>
       </c>
       <c r="N8" t="n">
-        <v>182.9193659245888</v>
+        <v>182.0128740328901</v>
       </c>
       <c r="O8" t="n">
-        <v>13.52476860891116</v>
+        <v>13.49121469819861</v>
       </c>
       <c r="P8" t="n">
-        <v>360.6000228571374</v>
+        <v>360.5926289648839</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21413,28 +21513,28 @@
         <v>0.0827</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1614703507717867</v>
+        <v>0.1602483526927632</v>
       </c>
       <c r="J9" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007612597026474988</v>
+        <v>0.007587907499220781</v>
       </c>
       <c r="M9" t="n">
-        <v>10.90945096421866</v>
+        <v>10.85958221297954</v>
       </c>
       <c r="N9" t="n">
-        <v>215.2600866236819</v>
+        <v>214.1917032658024</v>
       </c>
       <c r="O9" t="n">
-        <v>14.67174449830973</v>
+        <v>14.63528965431851</v>
       </c>
       <c r="P9" t="n">
-        <v>363.1011725813593</v>
+        <v>363.1122315265992</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21491,28 +21591,28 @@
         <v>0.0687</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2046933348645807</v>
+        <v>0.2041018845653967</v>
       </c>
       <c r="J10" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01446776961897189</v>
+        <v>0.01455504282333275</v>
       </c>
       <c r="M10" t="n">
-        <v>10.17756656743161</v>
+        <v>10.12957042541236</v>
       </c>
       <c r="N10" t="n">
-        <v>181.8097953234514</v>
+        <v>180.9116211585474</v>
       </c>
       <c r="O10" t="n">
-        <v>13.48368626613106</v>
+        <v>13.45033907225195</v>
       </c>
       <c r="P10" t="n">
-        <v>367.2911790902013</v>
+        <v>367.2964906369483</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21569,28 +21669,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1342988843300503</v>
+        <v>0.1346832878667713</v>
       </c>
       <c r="J11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006182352454961459</v>
+        <v>0.006294827724696805</v>
       </c>
       <c r="M11" t="n">
-        <v>10.11775279241102</v>
+        <v>10.06935938580138</v>
       </c>
       <c r="N11" t="n">
-        <v>180.7186576930036</v>
+        <v>179.8112655671665</v>
       </c>
       <c r="O11" t="n">
-        <v>13.44316397627447</v>
+        <v>13.40937230324993</v>
       </c>
       <c r="P11" t="n">
-        <v>369.8068929498316</v>
+        <v>369.8034085960995</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21647,28 +21747,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1354389549569047</v>
+        <v>0.1326426649102587</v>
       </c>
       <c r="J12" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K12" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006588684824362145</v>
+        <v>0.006395136512378219</v>
       </c>
       <c r="M12" t="n">
-        <v>10.05616179582665</v>
+        <v>10.01747611686629</v>
       </c>
       <c r="N12" t="n">
-        <v>174.2933896852168</v>
+        <v>173.4675277210629</v>
       </c>
       <c r="O12" t="n">
-        <v>13.20202218166659</v>
+        <v>13.17070718378717</v>
       </c>
       <c r="P12" t="n">
-        <v>371.2788680653341</v>
+        <v>371.3042501486594</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21725,28 +21825,28 @@
         <v>0.0911</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1308870978908298</v>
+        <v>0.1282394275658389</v>
       </c>
       <c r="J13" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K13" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007114824755186877</v>
+        <v>0.006912079897380963</v>
       </c>
       <c r="M13" t="n">
-        <v>9.360993110915446</v>
+        <v>9.324040826836313</v>
       </c>
       <c r="N13" t="n">
-        <v>149.030793801646</v>
+        <v>148.3220807327513</v>
       </c>
       <c r="O13" t="n">
-        <v>12.20781691383214</v>
+        <v>12.17875530309856</v>
       </c>
       <c r="P13" t="n">
-        <v>370.0343748131307</v>
+        <v>370.0586638780792</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21803,28 +21903,28 @@
         <v>0.0549</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2244133172318653</v>
+        <v>0.2247255060385563</v>
       </c>
       <c r="J14" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K14" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01303219522774945</v>
+        <v>0.01322612394926226</v>
       </c>
       <c r="M14" t="n">
-        <v>12.04965149101685</v>
+        <v>11.99095492834689</v>
       </c>
       <c r="N14" t="n">
-        <v>237.3982646036485</v>
+        <v>236.1997816565947</v>
       </c>
       <c r="O14" t="n">
-        <v>15.40773392175658</v>
+        <v>15.36879245928563</v>
       </c>
       <c r="P14" t="n">
-        <v>367.1841347381252</v>
+        <v>367.1812728013102</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -21881,28 +21981,28 @@
         <v>0.0408</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3301999695423933</v>
+        <v>0.3279561862719668</v>
       </c>
       <c r="J15" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K15" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01379416591309446</v>
+        <v>0.01378094000984997</v>
       </c>
       <c r="M15" t="n">
-        <v>17.19913475042694</v>
+        <v>17.1174531129807</v>
       </c>
       <c r="N15" t="n">
-        <v>474.9749511475541</v>
+        <v>472.5507809447632</v>
       </c>
       <c r="O15" t="n">
-        <v>21.79392005004043</v>
+        <v>21.73823316060354</v>
       </c>
       <c r="P15" t="n">
-        <v>362.18915486159</v>
+        <v>362.2099572328473</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -21959,28 +22059,28 @@
         <v>0.046</v>
       </c>
       <c r="I16" t="n">
-        <v>0.356627735374862</v>
+        <v>0.3591566564244816</v>
       </c>
       <c r="J16" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K16" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01833718710508325</v>
+        <v>0.01881121089403415</v>
       </c>
       <c r="M16" t="n">
-        <v>16.3607393480393</v>
+        <v>16.29388074357523</v>
       </c>
       <c r="N16" t="n">
-        <v>429.0651225162142</v>
+        <v>426.9642248072278</v>
       </c>
       <c r="O16" t="n">
-        <v>20.7138871899075</v>
+        <v>20.66311266017847</v>
       </c>
       <c r="P16" t="n">
-        <v>364.2404690060058</v>
+        <v>364.2175138462284</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22037,28 +22137,28 @@
         <v>0.0605</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3906481322145361</v>
+        <v>0.3905706085717109</v>
       </c>
       <c r="J17" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K17" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02978046574786386</v>
+        <v>0.03011613931164292</v>
       </c>
       <c r="M17" t="n">
-        <v>13.52164133676036</v>
+        <v>13.45465145415624</v>
       </c>
       <c r="N17" t="n">
-        <v>313.3093762369869</v>
+        <v>311.7506548412432</v>
       </c>
       <c r="O17" t="n">
-        <v>17.70054734286448</v>
+        <v>17.65646212697332</v>
       </c>
       <c r="P17" t="n">
-        <v>369.4021927794075</v>
+        <v>369.4028964659096</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22115,28 +22215,28 @@
         <v>0.0604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4068424878525669</v>
+        <v>0.4080964187399951</v>
       </c>
       <c r="J18" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K18" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04303622556024533</v>
+        <v>0.04378879936088076</v>
       </c>
       <c r="M18" t="n">
-        <v>12.20803881368245</v>
+        <v>12.15455939411196</v>
       </c>
       <c r="N18" t="n">
-        <v>229.4359378092897</v>
+        <v>228.2969316280262</v>
       </c>
       <c r="O18" t="n">
-        <v>15.14714289261475</v>
+        <v>15.10949806009539</v>
       </c>
       <c r="P18" t="n">
-        <v>372.595976156736</v>
+        <v>372.5844729085867</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22193,28 +22293,28 @@
         <v>0.0539</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2503477663491825</v>
+        <v>0.2493803565714362</v>
       </c>
       <c r="J19" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K19" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01816553535438359</v>
+        <v>0.0182403255726169</v>
       </c>
       <c r="M19" t="n">
-        <v>11.17674350327971</v>
+        <v>11.12532768939031</v>
       </c>
       <c r="N19" t="n">
-        <v>213.4719768596688</v>
+        <v>212.4148667339795</v>
       </c>
       <c r="O19" t="n">
-        <v>14.61068023261302</v>
+        <v>14.57445939765793</v>
       </c>
       <c r="P19" t="n">
-        <v>374.5945905594676</v>
+        <v>374.60337179288</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -22271,28 +22371,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4104003362768867</v>
+        <v>0.4074321198651091</v>
       </c>
       <c r="J20" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K20" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05317144881324676</v>
+        <v>0.05305627456130935</v>
       </c>
       <c r="M20" t="n">
-        <v>10.91691959804841</v>
+        <v>10.87296041140126</v>
       </c>
       <c r="N20" t="n">
-        <v>185.725196112007</v>
+        <v>184.8262483476632</v>
       </c>
       <c r="O20" t="n">
-        <v>13.62810317366313</v>
+        <v>13.59508177053978</v>
       </c>
       <c r="P20" t="n">
-        <v>369.2417624563565</v>
+        <v>369.2689171076395</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -22349,28 +22449,28 @@
         <v>0.0654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1390539435733331</v>
+        <v>0.1411955803725185</v>
       </c>
       <c r="J21" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K21" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007133569595250688</v>
+        <v>0.007439151178389114</v>
       </c>
       <c r="M21" t="n">
-        <v>10.0074259798865</v>
+        <v>9.971623327323144</v>
       </c>
       <c r="N21" t="n">
-        <v>173.1848733497358</v>
+        <v>172.3395700105996</v>
       </c>
       <c r="O21" t="n">
-        <v>13.15997239167833</v>
+        <v>13.1278166505554</v>
       </c>
       <c r="P21" t="n">
-        <v>375.6969053098443</v>
+        <v>375.677701739143</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -22427,28 +22527,28 @@
         <v>0.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2021910364123111</v>
+        <v>0.2022221213075937</v>
       </c>
       <c r="J22" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K22" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01526183882958321</v>
+        <v>0.01544340914822262</v>
       </c>
       <c r="M22" t="n">
-        <v>10.06166001467173</v>
+        <v>10.01184869644386</v>
       </c>
       <c r="N22" t="n">
-        <v>168.7920765786731</v>
+        <v>167.9523202912722</v>
       </c>
       <c r="O22" t="n">
-        <v>12.99200048409301</v>
+        <v>12.95964198160089</v>
       </c>
       <c r="P22" t="n">
-        <v>371.9241506141183</v>
+        <v>371.9238702654723</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -22505,28 +22605,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.00125559748416028</v>
+        <v>0.0009994649780120355</v>
       </c>
       <c r="J23" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K23" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L23" t="n">
-        <v>6.413669355609386e-07</v>
+        <v>4.111697395892122e-07</v>
       </c>
       <c r="M23" t="n">
-        <v>9.383487195487433</v>
+        <v>9.337049776710515</v>
       </c>
       <c r="N23" t="n">
-        <v>156.1202151710523</v>
+        <v>155.3360478982336</v>
       </c>
       <c r="O23" t="n">
-        <v>12.49480752837163</v>
+        <v>12.46338829926411</v>
       </c>
       <c r="P23" t="n">
-        <v>375.0852572077624</v>
+        <v>375.0875932691795</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -22583,28 +22683,28 @@
         <v>0.0519</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01968808494437542</v>
+        <v>0.02122050087228126</v>
       </c>
       <c r="J24" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K24" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0002090463827583156</v>
+        <v>0.0002456832681442256</v>
       </c>
       <c r="M24" t="n">
-        <v>8.535473993829577</v>
+        <v>8.50359351742846</v>
       </c>
       <c r="N24" t="n">
-        <v>117.3132991053016</v>
+        <v>116.739418271843</v>
       </c>
       <c r="O24" t="n">
-        <v>10.83112640057818</v>
+        <v>10.80460171740926</v>
       </c>
       <c r="P24" t="n">
-        <v>379.8682308517377</v>
+        <v>379.8542436995081</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -22661,28 +22761,28 @@
         <v>0.0529</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1345782736307594</v>
+        <v>-0.1293685223746854</v>
       </c>
       <c r="J25" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K25" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L25" t="n">
-        <v>0.007184879378071551</v>
+        <v>0.006714559390052943</v>
       </c>
       <c r="M25" t="n">
-        <v>10.19194000631694</v>
+        <v>10.17830961904154</v>
       </c>
       <c r="N25" t="n">
-        <v>159.0978674230492</v>
+        <v>158.4376214709845</v>
       </c>
       <c r="O25" t="n">
-        <v>12.61340031169427</v>
+        <v>12.58720070035369</v>
       </c>
       <c r="P25" t="n">
-        <v>392.4228971648914</v>
+        <v>392.3752688214192</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -22739,28 +22839,28 @@
         <v>0.042</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.08345383694864517</v>
+        <v>-0.0790955335229129</v>
       </c>
       <c r="J26" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K26" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001838625009752737</v>
+        <v>0.001670821508848563</v>
       </c>
       <c r="M26" t="n">
-        <v>12.6692378722149</v>
+        <v>12.63190558230783</v>
       </c>
       <c r="N26" t="n">
-        <v>234.7103265090986</v>
+        <v>233.6306317103665</v>
       </c>
       <c r="O26" t="n">
-        <v>15.32025869589344</v>
+        <v>15.28498059241053</v>
       </c>
       <c r="P26" t="n">
-        <v>385.4870305476865</v>
+        <v>385.4465878167873</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -22821,28 +22921,28 @@
         <v>0.0332</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0124623047841023</v>
+        <v>0.01422778404246165</v>
       </c>
       <c r="J27" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K27" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L27" t="n">
-        <v>4.024155937809581e-05</v>
+        <v>5.307045583824443e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>12.73168683032917</v>
+        <v>12.67923875840667</v>
       </c>
       <c r="N27" t="n">
-        <v>244.5889403773054</v>
+        <v>243.3703618535239</v>
       </c>
       <c r="O27" t="n">
-        <v>15.63933951218226</v>
+        <v>15.60033210715477</v>
       </c>
       <c r="P27" t="n">
-        <v>382.2312353656434</v>
+        <v>382.2151354454531</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -22884,7 +22984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB204"/>
+  <dimension ref="A1:AB205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51305,7 +51405,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-34.712822790063626,173.072313844978</t>
+          <t>-34.712791196264014,173.0723578558755</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -51414,6 +51514,148 @@
         </is>
       </c>
       <c r="AB204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>-34.710384249710785,173.07024802825632</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>-34.710963568368854,173.07080672165296</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>-34.71150294770651,173.07142104597216</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-34.71207007121406,173.07199671699354</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-34.71261263774714,173.07260659099285</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-34.713194176697975,173.07316214945044</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-34.713752815569364,173.07374955636624</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-34.7142951398063,173.07435931557777</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-34.71480993692132,173.0750064648378</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-34.715350672662844,173.07561841819813</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-34.71591149013851,173.07620167743872</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-34.71645581396428,173.07680312937785</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-34.71694402632202,173.07747462733204</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-34.717481890543866,173.07809236334805</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>-34.71793941702521,173.07880209027786</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>-34.71842459208001,173.0794801532001</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>-34.71889375737947,173.08016408460378</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>-34.71938188927648,173.08082668273352</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>-34.719861562670516,173.08150972690035</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>-34.72028437004729,173.0822386000732</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>-34.72072277661408,173.08294809796797</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>-34.72112616065451,173.08369738234234</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>-34.72145702095776,173.08450410756853</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>-34.72173558387238,173.08531317562287</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>-34.722037169161645,173.08608784333637</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>-34.722283680573085,173.0869272925718</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0012/nzd0012.xlsx
+++ b/data/nzd0012/nzd0012.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB205"/>
+  <dimension ref="A1:AB206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18554,7 +18554,7 @@
         <v>339.88</v>
       </c>
       <c r="F204" t="n">
-        <v>339.15</v>
+        <v>333.81</v>
       </c>
       <c r="G204" t="n">
         <v>345.8</v>
@@ -18643,9 +18643,7 @@
       <c r="E205" t="n">
         <v>366.87</v>
       </c>
-      <c r="F205" t="n">
-        <v>369.33</v>
-      </c>
+      <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
         <v>365.2</v>
       </c>
@@ -18712,6 +18710,96 @@
       <c r="AB205" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="C206" t="n">
+        <v>364.79</v>
+      </c>
+      <c r="D206" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="E206" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="F206" t="n">
+        <v>337.87</v>
+      </c>
+      <c r="G206" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="H206" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="I206" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="J206" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="K206" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="L206" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="M206" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="N206" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="O206" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="P206" t="n">
+        <v>383.63</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>375.72</v>
+      </c>
+      <c r="R206" t="n">
+        <v>379.87</v>
+      </c>
+      <c r="S206" t="n">
+        <v>378.34</v>
+      </c>
+      <c r="T206" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="U206" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="V206" t="n">
+        <v>373.96</v>
+      </c>
+      <c r="W206" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="X206" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>389.16</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B207"/>
+  <dimension ref="A1:B208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20799,6 +20887,16 @@
       </c>
       <c r="B207" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -20967,28 +21065,28 @@
         <v>0.0363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1181638229119615</v>
+        <v>0.1195582712131309</v>
       </c>
       <c r="J2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004343803983496652</v>
+        <v>0.004499092488161605</v>
       </c>
       <c r="M2" t="n">
-        <v>10.96523969664861</v>
+        <v>10.91829210981017</v>
       </c>
       <c r="N2" t="n">
-        <v>203.9720599817977</v>
+        <v>202.97274870959</v>
       </c>
       <c r="O2" t="n">
-        <v>14.28187872731727</v>
+        <v>14.24685048386449</v>
       </c>
       <c r="P2" t="n">
-        <v>358.9990664963053</v>
+        <v>358.9863225887678</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21045,28 +21143,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1358279170132083</v>
+        <v>0.1352743297723251</v>
       </c>
       <c r="J3" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00820068735724333</v>
+        <v>0.008230333473422391</v>
       </c>
       <c r="M3" t="n">
-        <v>9.081295513265157</v>
+        <v>9.039817942829609</v>
       </c>
       <c r="N3" t="n">
-        <v>143.7419286292775</v>
+        <v>143.0355124615898</v>
       </c>
       <c r="O3" t="n">
-        <v>11.98924220412939</v>
+        <v>11.95974550153931</v>
       </c>
       <c r="P3" t="n">
-        <v>361.7572903006384</v>
+        <v>361.7622959650617</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21123,28 +21221,28 @@
         <v>0.0382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.141568118554382</v>
+        <v>0.1437621652766534</v>
       </c>
       <c r="J4" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01099114388140154</v>
+        <v>0.01146174803847955</v>
       </c>
       <c r="M4" t="n">
-        <v>7.73369853495586</v>
+        <v>7.704685666917524</v>
       </c>
       <c r="N4" t="n">
-        <v>114.9345612651518</v>
+        <v>114.3914521601576</v>
       </c>
       <c r="O4" t="n">
-        <v>10.72075376385223</v>
+        <v>10.69539396937567</v>
       </c>
       <c r="P4" t="n">
-        <v>363.3811531363179</v>
+        <v>363.3611016732853</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21201,28 +21299,28 @@
         <v>0.0403</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1482144726059892</v>
+        <v>0.1501299061214047</v>
       </c>
       <c r="J5" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K5" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007049468227598887</v>
+        <v>0.007316505808610207</v>
       </c>
       <c r="M5" t="n">
-        <v>10.39133384370178</v>
+        <v>10.35026412034037</v>
       </c>
       <c r="N5" t="n">
-        <v>197.2036348392912</v>
+        <v>196.247099081814</v>
       </c>
       <c r="O5" t="n">
-        <v>14.04292116474671</v>
+        <v>14.00882218752933</v>
       </c>
       <c r="P5" t="n">
-        <v>357.366607913834</v>
+        <v>357.3491027057927</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21279,28 +21377,28 @@
         <v>0.0402</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3046725408499127</v>
+        <v>0.2692330748388674</v>
       </c>
       <c r="J6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K6" t="n">
         <v>201</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02324225899676713</v>
+        <v>0.01797240478249917</v>
       </c>
       <c r="M6" t="n">
-        <v>11.92918720371402</v>
+        <v>12.01297848807836</v>
       </c>
       <c r="N6" t="n">
-        <v>248.6208738546381</v>
+        <v>252.5020006343737</v>
       </c>
       <c r="O6" t="n">
-        <v>15.76771619019819</v>
+        <v>15.89031153358466</v>
       </c>
       <c r="P6" t="n">
-        <v>353.9168239765391</v>
+        <v>354.2396071916255</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21357,28 +21455,28 @@
         <v>0.0688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1310278286295921</v>
+        <v>0.1292615343359894</v>
       </c>
       <c r="J7" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K7" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004986854927669371</v>
+        <v>0.004911253517793979</v>
       </c>
       <c r="M7" t="n">
-        <v>11.2098577651525</v>
+        <v>11.16312240070321</v>
       </c>
       <c r="N7" t="n">
-        <v>218.3190366133107</v>
+        <v>217.2550178647836</v>
       </c>
       <c r="O7" t="n">
-        <v>14.77562305330339</v>
+        <v>14.73957319140495</v>
       </c>
       <c r="P7" t="n">
-        <v>357.9138254487884</v>
+        <v>357.9299676687208</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21435,28 +21533,28 @@
         <v>0.0762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1243829887503318</v>
+        <v>0.1214224790270744</v>
       </c>
       <c r="J8" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K8" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005388103785957221</v>
+        <v>0.005195625899432676</v>
       </c>
       <c r="M8" t="n">
-        <v>10.36710598651931</v>
+        <v>10.32984333100167</v>
       </c>
       <c r="N8" t="n">
-        <v>182.0128740328901</v>
+        <v>181.1589290679383</v>
       </c>
       <c r="O8" t="n">
-        <v>13.49121469819861</v>
+        <v>13.45952930335747</v>
       </c>
       <c r="P8" t="n">
-        <v>360.5926289648839</v>
+        <v>360.6196851577494</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21513,28 +21611,28 @@
         <v>0.0827</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1602483526927632</v>
+        <v>0.1544646806663998</v>
       </c>
       <c r="J9" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007587907499220781</v>
+        <v>0.007132428430604687</v>
       </c>
       <c r="M9" t="n">
-        <v>10.85958221297954</v>
+        <v>10.82761072709102</v>
       </c>
       <c r="N9" t="n">
-        <v>214.1917032658024</v>
+        <v>213.3041600567641</v>
       </c>
       <c r="O9" t="n">
-        <v>14.63528965431851</v>
+        <v>14.6049361538065</v>
       </c>
       <c r="P9" t="n">
-        <v>363.1122315265992</v>
+        <v>363.1649433893678</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21591,28 +21689,28 @@
         <v>0.0687</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2041018845653967</v>
+        <v>0.1995176618838136</v>
       </c>
       <c r="J10" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K10" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01455504282333275</v>
+        <v>0.01407358144607107</v>
       </c>
       <c r="M10" t="n">
-        <v>10.12957042541236</v>
+        <v>10.09785468853134</v>
       </c>
       <c r="N10" t="n">
-        <v>180.9116211585474</v>
+        <v>180.1334963635481</v>
       </c>
       <c r="O10" t="n">
-        <v>13.45033907225195</v>
+        <v>13.42138205862377</v>
       </c>
       <c r="P10" t="n">
-        <v>367.2964906369483</v>
+        <v>367.3379514267676</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21669,28 +21767,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1346832878667713</v>
+        <v>0.1337428968615103</v>
       </c>
       <c r="J11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006294827724696805</v>
+        <v>0.006284939836324055</v>
       </c>
       <c r="M11" t="n">
-        <v>10.06935938580138</v>
+        <v>10.02247888391595</v>
       </c>
       <c r="N11" t="n">
-        <v>179.8112655671665</v>
+        <v>178.9166726252445</v>
       </c>
       <c r="O11" t="n">
-        <v>13.40937230324993</v>
+        <v>13.37597370755656</v>
       </c>
       <c r="P11" t="n">
-        <v>369.8034085960995</v>
+        <v>369.8119908196535</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21747,28 +21845,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1326426649102587</v>
+        <v>0.1291994966944453</v>
       </c>
       <c r="J12" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K12" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006395136512378219</v>
+        <v>0.006139938919534349</v>
       </c>
       <c r="M12" t="n">
-        <v>10.01747611686629</v>
+        <v>9.981842350913508</v>
       </c>
       <c r="N12" t="n">
-        <v>173.4675277210629</v>
+        <v>172.6716070840755</v>
       </c>
       <c r="O12" t="n">
-        <v>13.17070718378717</v>
+        <v>13.14045688262305</v>
       </c>
       <c r="P12" t="n">
-        <v>371.3042501486594</v>
+        <v>371.3357234151955</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21825,28 +21923,28 @@
         <v>0.0911</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1282394275658389</v>
+        <v>0.1246579566378893</v>
       </c>
       <c r="J13" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006912079897380963</v>
+        <v>0.006609512051758748</v>
       </c>
       <c r="M13" t="n">
-        <v>9.324040826836313</v>
+        <v>9.291018256669558</v>
       </c>
       <c r="N13" t="n">
-        <v>148.3220807327513</v>
+        <v>147.6511118032655</v>
       </c>
       <c r="O13" t="n">
-        <v>12.17875530309856</v>
+        <v>12.15117738341703</v>
       </c>
       <c r="P13" t="n">
-        <v>370.0586638780792</v>
+        <v>370.0917477859531</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21903,28 +22001,28 @@
         <v>0.0549</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2247255060385563</v>
+        <v>0.219789335155417</v>
       </c>
       <c r="J14" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K14" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01322612394926226</v>
+        <v>0.0128056769548196</v>
       </c>
       <c r="M14" t="n">
-        <v>11.99095492834689</v>
+        <v>11.94709798150191</v>
       </c>
       <c r="N14" t="n">
-        <v>236.1997816565947</v>
+        <v>235.1379659154421</v>
       </c>
       <c r="O14" t="n">
-        <v>15.36879245928563</v>
+        <v>15.33420900846999</v>
       </c>
       <c r="P14" t="n">
-        <v>367.1812728013102</v>
+        <v>367.2268374585814</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -21981,28 +22079,28 @@
         <v>0.0408</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3279561862719668</v>
+        <v>0.3307465231045027</v>
       </c>
       <c r="J15" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K15" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01378094000984997</v>
+        <v>0.01418913023183643</v>
       </c>
       <c r="M15" t="n">
-        <v>17.1174531129807</v>
+        <v>17.04870961543965</v>
       </c>
       <c r="N15" t="n">
-        <v>472.5507809447632</v>
+        <v>470.1650125012078</v>
       </c>
       <c r="O15" t="n">
-        <v>21.73823316060354</v>
+        <v>21.6832887842506</v>
       </c>
       <c r="P15" t="n">
-        <v>362.2099572328473</v>
+        <v>362.1839144318674</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22059,28 +22157,28 @@
         <v>0.046</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3591566564244816</v>
+        <v>0.3685781521672938</v>
       </c>
       <c r="J16" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K16" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01881121089403415</v>
+        <v>0.02000345591710817</v>
       </c>
       <c r="M16" t="n">
-        <v>16.29388074357523</v>
+        <v>16.2664279054307</v>
       </c>
       <c r="N16" t="n">
-        <v>426.9642248072278</v>
+        <v>425.3209616729197</v>
       </c>
       <c r="O16" t="n">
-        <v>20.66311266017847</v>
+        <v>20.62331112292397</v>
       </c>
       <c r="P16" t="n">
-        <v>364.2175138462284</v>
+        <v>364.1313939624189</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22137,28 +22235,28 @@
         <v>0.0605</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3905706085717109</v>
+        <v>0.3866423123988037</v>
       </c>
       <c r="J17" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K17" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03011613931164292</v>
+        <v>0.02986900104399515</v>
       </c>
       <c r="M17" t="n">
-        <v>13.45465145415624</v>
+        <v>13.40233456790475</v>
       </c>
       <c r="N17" t="n">
-        <v>311.7506548412432</v>
+        <v>310.2891163618872</v>
       </c>
       <c r="O17" t="n">
-        <v>17.65646212697332</v>
+        <v>17.61502530119918</v>
       </c>
       <c r="P17" t="n">
-        <v>369.4028964659096</v>
+        <v>369.4388041836664</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22215,28 +22313,28 @@
         <v>0.0604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4080964187399951</v>
+        <v>0.4046100781843863</v>
       </c>
       <c r="J18" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K18" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04378879936088076</v>
+        <v>0.04356326950982903</v>
       </c>
       <c r="M18" t="n">
-        <v>12.15455939411196</v>
+        <v>12.10866629784796</v>
       </c>
       <c r="N18" t="n">
-        <v>228.2969316280262</v>
+        <v>227.2245683782403</v>
       </c>
       <c r="O18" t="n">
-        <v>15.10949806009539</v>
+        <v>15.07396989443194</v>
       </c>
       <c r="P18" t="n">
-        <v>372.5844729085867</v>
+        <v>372.6166780477823</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22293,28 +22391,28 @@
         <v>0.0539</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2493803565714362</v>
+        <v>0.2465887917171337</v>
       </c>
       <c r="J19" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K19" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0182403255726169</v>
+        <v>0.01804928520437499</v>
       </c>
       <c r="M19" t="n">
-        <v>11.12532768939031</v>
+        <v>11.08213785253842</v>
       </c>
       <c r="N19" t="n">
-        <v>212.4148667339795</v>
+        <v>211.4046072760918</v>
       </c>
       <c r="O19" t="n">
-        <v>14.57445939765793</v>
+        <v>14.5397595329528</v>
       </c>
       <c r="P19" t="n">
-        <v>374.60337179288</v>
+        <v>374.6288888920182</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -22371,28 +22469,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4074321198651091</v>
+        <v>0.3974149057952551</v>
       </c>
       <c r="J20" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K20" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05305627456130935</v>
+        <v>0.05108118555999031</v>
       </c>
       <c r="M20" t="n">
-        <v>10.87296041140126</v>
+        <v>10.85611063555949</v>
       </c>
       <c r="N20" t="n">
-        <v>184.8262483476632</v>
+        <v>184.394508554672</v>
       </c>
       <c r="O20" t="n">
-        <v>13.59508177053978</v>
+        <v>13.57919395820945</v>
       </c>
       <c r="P20" t="n">
-        <v>369.2689171076395</v>
+        <v>369.3611841275537</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -22449,28 +22547,28 @@
         <v>0.0654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1411955803725185</v>
+        <v>0.1432430196658321</v>
       </c>
       <c r="J21" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K21" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007439151178389114</v>
+        <v>0.007744421869071649</v>
       </c>
       <c r="M21" t="n">
-        <v>9.971623327323144</v>
+        <v>9.935403597051961</v>
       </c>
       <c r="N21" t="n">
-        <v>172.3395700105996</v>
+        <v>171.5007857691248</v>
       </c>
       <c r="O21" t="n">
-        <v>13.1278166505554</v>
+        <v>13.09583085447902</v>
       </c>
       <c r="P21" t="n">
-        <v>375.677701739143</v>
+        <v>375.659209662376</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -22527,28 +22625,28 @@
         <v>0.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2022221213075937</v>
+        <v>0.1990597362466408</v>
       </c>
       <c r="J22" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K22" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01544340914822262</v>
+        <v>0.01514059063589257</v>
       </c>
       <c r="M22" t="n">
-        <v>10.01184869644386</v>
+        <v>9.970235801471906</v>
       </c>
       <c r="N22" t="n">
-        <v>167.9523202912722</v>
+        <v>167.1757930904079</v>
       </c>
       <c r="O22" t="n">
-        <v>12.95964198160089</v>
+        <v>12.9296478331936</v>
       </c>
       <c r="P22" t="n">
-        <v>371.9238702654723</v>
+        <v>371.952596977674</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -22605,28 +22703,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0009994649780120355</v>
+        <v>0.0006566859375861678</v>
       </c>
       <c r="J23" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K23" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L23" t="n">
-        <v>4.111697395892122e-07</v>
+        <v>1.795965166584423e-07</v>
       </c>
       <c r="M23" t="n">
-        <v>9.337049776710515</v>
+        <v>9.291297381025192</v>
       </c>
       <c r="N23" t="n">
-        <v>155.3360478982336</v>
+        <v>154.5600081669296</v>
       </c>
       <c r="O23" t="n">
-        <v>12.46338829926411</v>
+        <v>12.43221654279436</v>
       </c>
       <c r="P23" t="n">
-        <v>375.0875932691795</v>
+        <v>375.090742126646</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -22683,28 +22781,28 @@
         <v>0.0519</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02122050087228126</v>
+        <v>0.02075781239173121</v>
       </c>
       <c r="J24" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K24" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0002456832681442256</v>
+        <v>0.0002378675589984613</v>
       </c>
       <c r="M24" t="n">
-        <v>8.50359351742846</v>
+        <v>8.462841609117039</v>
       </c>
       <c r="N24" t="n">
-        <v>116.739418271843</v>
+        <v>116.1597855996679</v>
       </c>
       <c r="O24" t="n">
-        <v>10.80460171740926</v>
+        <v>10.77774492181309</v>
       </c>
       <c r="P24" t="n">
-        <v>379.8542436995081</v>
+        <v>379.8584970996233</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -22761,28 +22859,28 @@
         <v>0.0529</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1293685223746854</v>
+        <v>-0.129143210901955</v>
       </c>
       <c r="J25" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K25" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L25" t="n">
-        <v>0.006714559390052943</v>
+        <v>0.006769935211141886</v>
       </c>
       <c r="M25" t="n">
-        <v>10.17830961904154</v>
+        <v>10.12852797904706</v>
       </c>
       <c r="N25" t="n">
-        <v>158.4376214709845</v>
+        <v>157.6377080064858</v>
       </c>
       <c r="O25" t="n">
-        <v>12.58720070035369</v>
+        <v>12.55538561759398</v>
       </c>
       <c r="P25" t="n">
-        <v>392.3752688214192</v>
+        <v>392.373194050017</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -22839,28 +22937,28 @@
         <v>0.042</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0790955335229129</v>
+        <v>-0.08146496011052437</v>
       </c>
       <c r="J26" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K26" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001670821508848563</v>
+        <v>0.001793141997944114</v>
       </c>
       <c r="M26" t="n">
-        <v>12.63190558230783</v>
+        <v>12.5787924016656</v>
       </c>
       <c r="N26" t="n">
-        <v>233.6306317103665</v>
+        <v>232.4920651120133</v>
       </c>
       <c r="O26" t="n">
-        <v>15.28498059241053</v>
+        <v>15.24769048452956</v>
       </c>
       <c r="P26" t="n">
-        <v>385.4465878167873</v>
+        <v>385.4687288749338</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -22921,28 +23019,28 @@
         <v>0.0332</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01422778404246165</v>
+        <v>0.01316949755743339</v>
       </c>
       <c r="J27" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K27" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L27" t="n">
-        <v>5.307045583824443e-05</v>
+        <v>4.601089142797221e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>12.67923875840667</v>
+        <v>12.61943898356177</v>
       </c>
       <c r="N27" t="n">
-        <v>243.3703618535239</v>
+        <v>242.1534249031184</v>
       </c>
       <c r="O27" t="n">
-        <v>15.60033210715477</v>
+        <v>15.56127966791672</v>
       </c>
       <c r="P27" t="n">
-        <v>382.2151354454531</v>
+        <v>382.224855459126</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -22984,7 +23082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB205"/>
+  <dimension ref="A1:AB206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51405,7 +51503,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-34.712791196264014,173.0723578558755</t>
+          <t>-34.712822790063626,173.072313844978</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -51545,11 +51643,7 @@
           <t>-34.71207007121406,173.07199671699354</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>-34.71261263774714,173.07260659099285</t>
-        </is>
-      </c>
+      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
           <t>-34.713194176697975,173.07316214945044</t>
@@ -51658,6 +51752,148 @@
       <c r="AB205" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>-34.71041791378444,173.0702011335848</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>-34.71096812398301,173.0708003756027</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>-34.711497622937976,173.07142846345457</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-34.71209101538553,173.07196754144772</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-34.712798769311064,173.07234730644996</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-34.71322765241146,173.0731156337939</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-34.713776275046655,173.0737173865168</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-34.714323784505346,173.07432045332206</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-34.714835098738014,173.07497232789444</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-34.715358599571665,173.0756076638096</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-34.71591586822527,173.0761958707592</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-34.716462171049514,173.0767953834044</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-34.716978820351336,173.07743478468458</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-34.71744958635601,173.0781293547906</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>-34.71789158302187,173.07885686463877</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>-34.71845054048543,173.07945043992586</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>-34.718926450267965,173.080129560064</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>-34.71939521300078,173.08081381038886</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>-34.71991161093777,173.08146171540395</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>-34.72028458847271,173.08223840675012</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>-34.72074826795565,173.08292826068052</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>-34.72112692943371,173.08369681144643</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>-34.721472934737626,173.08449229007724</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>-34.72177712064058,173.08528850795895</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>-34.72209592034636,173.08606335536155</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>-34.72230873607423,173.08691784400332</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0012/nzd0012.xlsx
+++ b/data/nzd0012/nzd0012.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB206"/>
+  <dimension ref="A1:AB208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18759,10 +18759,10 @@
         <v>368.14</v>
       </c>
       <c r="O206" t="n">
-        <v>373.69</v>
+        <v>360.54</v>
       </c>
       <c r="P206" t="n">
-        <v>383.63</v>
+        <v>371.45</v>
       </c>
       <c r="Q206" t="n">
         <v>375.72</v>
@@ -18800,6 +18800,186 @@
       <c r="AB206" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="C207" t="n">
+        <v>355.73</v>
+      </c>
+      <c r="D207" t="n">
+        <v>362.04</v>
+      </c>
+      <c r="E207" t="n">
+        <v>356.08</v>
+      </c>
+      <c r="F207" t="n">
+        <v>336.41</v>
+      </c>
+      <c r="G207" t="n">
+        <v>353.56</v>
+      </c>
+      <c r="H207" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="I207" t="n">
+        <v>356.97</v>
+      </c>
+      <c r="J207" t="n">
+        <v>361.18</v>
+      </c>
+      <c r="K207" t="n">
+        <v>365.67</v>
+      </c>
+      <c r="L207" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="M207" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="N207" t="n">
+        <v>362.66</v>
+      </c>
+      <c r="O207" t="n">
+        <v>360.54</v>
+      </c>
+      <c r="P207" t="n">
+        <v>364.71</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>369.32</v>
+      </c>
+      <c r="R207" t="n">
+        <v>372.35</v>
+      </c>
+      <c r="S207" t="n">
+        <v>371.95</v>
+      </c>
+      <c r="T207" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="U207" t="n">
+        <v>374.67</v>
+      </c>
+      <c r="V207" t="n">
+        <v>367.85</v>
+      </c>
+      <c r="W207" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="X207" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>381.14</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>374.02</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>346.48</v>
+      </c>
+      <c r="C208" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="D208" t="n">
+        <v>357</v>
+      </c>
+      <c r="E208" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="F208" t="n">
+        <v>328.31</v>
+      </c>
+      <c r="G208" t="n">
+        <v>348.61</v>
+      </c>
+      <c r="H208" t="n">
+        <v>351.43</v>
+      </c>
+      <c r="I208" t="n">
+        <v>353.06</v>
+      </c>
+      <c r="J208" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="K208" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="L208" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="M208" t="n">
+        <v>360.93</v>
+      </c>
+      <c r="N208" t="n">
+        <v>356.55</v>
+      </c>
+      <c r="O208" t="n">
+        <v>348.83</v>
+      </c>
+      <c r="P208" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>365.28</v>
+      </c>
+      <c r="R208" t="n">
+        <v>367.53</v>
+      </c>
+      <c r="S208" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="T208" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="U208" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="V208" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="W208" t="n">
+        <v>365.58</v>
+      </c>
+      <c r="X208" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>371.33</v>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18814,7 +18994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B208"/>
+  <dimension ref="A1:B210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20897,6 +21077,26 @@
       </c>
       <c r="B208" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -21065,28 +21265,28 @@
         <v>0.0363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1195582712131309</v>
+        <v>0.09702337233386746</v>
       </c>
       <c r="J2" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004499092488161605</v>
+        <v>0.003013868172010326</v>
       </c>
       <c r="M2" t="n">
-        <v>10.91829210981017</v>
+        <v>10.92691362008363</v>
       </c>
       <c r="N2" t="n">
-        <v>202.97274870959</v>
+        <v>202.5129309162983</v>
       </c>
       <c r="O2" t="n">
-        <v>14.24685048386449</v>
+        <v>14.23070380959066</v>
       </c>
       <c r="P2" t="n">
-        <v>358.9863225887678</v>
+        <v>359.1927461088764</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21143,28 +21343,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1352743297723251</v>
+        <v>0.1124672877655572</v>
       </c>
       <c r="J3" t="n">
+        <v>207</v>
+      </c>
+      <c r="K3" t="n">
         <v>205</v>
       </c>
-      <c r="K3" t="n">
-        <v>203</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.008230333473422391</v>
+        <v>0.005773243231928404</v>
       </c>
       <c r="M3" t="n">
-        <v>9.039817942829609</v>
+        <v>9.085475176129981</v>
       </c>
       <c r="N3" t="n">
-        <v>143.0355124615898</v>
+        <v>143.1825648681899</v>
       </c>
       <c r="O3" t="n">
-        <v>11.95974550153931</v>
+        <v>11.96589172891807</v>
       </c>
       <c r="P3" t="n">
-        <v>361.7622959650617</v>
+        <v>361.96899083684</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21221,28 +21421,28 @@
         <v>0.0382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1437621652766534</v>
+        <v>0.1295519450138916</v>
       </c>
       <c r="J4" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K4" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01146174803847955</v>
+        <v>0.009492599199999452</v>
       </c>
       <c r="M4" t="n">
-        <v>7.704685666917524</v>
+        <v>7.717960379021935</v>
       </c>
       <c r="N4" t="n">
-        <v>114.3914521601576</v>
+        <v>113.8926290754309</v>
       </c>
       <c r="O4" t="n">
-        <v>10.69539396937567</v>
+        <v>10.67204896331679</v>
       </c>
       <c r="P4" t="n">
-        <v>363.3611016732853</v>
+        <v>363.4912751073726</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21299,28 +21499,28 @@
         <v>0.0403</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1501299061214047</v>
+        <v>0.1339411042322107</v>
       </c>
       <c r="J5" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K5" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007316505808610207</v>
+        <v>0.005942437373034681</v>
       </c>
       <c r="M5" t="n">
-        <v>10.35026412034037</v>
+        <v>10.32966665679805</v>
       </c>
       <c r="N5" t="n">
-        <v>196.247099081814</v>
+        <v>195.1685487756023</v>
       </c>
       <c r="O5" t="n">
-        <v>14.00882218752933</v>
+        <v>13.97027375449752</v>
       </c>
       <c r="P5" t="n">
-        <v>357.3491027057927</v>
+        <v>357.4974115771424</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21377,28 +21577,28 @@
         <v>0.0402</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2692330748388674</v>
+        <v>0.2146278549109991</v>
       </c>
       <c r="J6" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K6" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01797240478249917</v>
+        <v>0.01139840901326061</v>
       </c>
       <c r="M6" t="n">
-        <v>12.01297848807836</v>
+        <v>12.14745722309795</v>
       </c>
       <c r="N6" t="n">
-        <v>252.5020006343737</v>
+        <v>258.2294558882888</v>
       </c>
       <c r="O6" t="n">
-        <v>15.89031153358466</v>
+        <v>16.06951946662652</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2396071916255</v>
+        <v>354.7396474436281</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21455,28 +21655,28 @@
         <v>0.0688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1292615343359894</v>
+        <v>0.1102281625474089</v>
       </c>
       <c r="J7" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K7" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004911253517793979</v>
+        <v>0.003641658311364315</v>
       </c>
       <c r="M7" t="n">
-        <v>11.16312240070321</v>
+        <v>11.14713414578971</v>
       </c>
       <c r="N7" t="n">
-        <v>217.2550178647836</v>
+        <v>216.190529470897</v>
       </c>
       <c r="O7" t="n">
-        <v>14.73957319140495</v>
+        <v>14.70341897216076</v>
       </c>
       <c r="P7" t="n">
-        <v>357.9299676687208</v>
+        <v>358.1043079910525</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21533,28 +21733,28 @@
         <v>0.0762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1214224790270744</v>
+        <v>0.1028260599335324</v>
       </c>
       <c r="J8" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K8" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005195625899432676</v>
+        <v>0.003797151410229405</v>
       </c>
       <c r="M8" t="n">
-        <v>10.32984333100167</v>
+        <v>10.3183616433244</v>
       </c>
       <c r="N8" t="n">
-        <v>181.1589290679383</v>
+        <v>180.3978747177241</v>
       </c>
       <c r="O8" t="n">
-        <v>13.45952930335747</v>
+        <v>13.43122759533633</v>
       </c>
       <c r="P8" t="n">
-        <v>360.6196851577494</v>
+        <v>360.7900223322084</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21611,28 +21811,28 @@
         <v>0.0827</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1544646806663998</v>
+        <v>0.1316129192168671</v>
       </c>
       <c r="J9" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K9" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007132428430604687</v>
+        <v>0.005273765716647616</v>
       </c>
       <c r="M9" t="n">
-        <v>10.82761072709102</v>
+        <v>10.8070879108487</v>
       </c>
       <c r="N9" t="n">
-        <v>213.3041600567641</v>
+        <v>212.6765824507026</v>
       </c>
       <c r="O9" t="n">
-        <v>14.6049361538065</v>
+        <v>14.58343520747779</v>
       </c>
       <c r="P9" t="n">
-        <v>363.1649433893678</v>
+        <v>363.3736650165815</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21689,28 +21889,28 @@
         <v>0.0687</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1995176618838136</v>
+        <v>0.1736503542364086</v>
       </c>
       <c r="J10" t="n">
+        <v>207</v>
+      </c>
+      <c r="K10" t="n">
         <v>205</v>
       </c>
-      <c r="K10" t="n">
-        <v>203</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.01407358144607107</v>
+        <v>0.01083103184422407</v>
       </c>
       <c r="M10" t="n">
-        <v>10.09785468853134</v>
+        <v>10.10053526731317</v>
       </c>
       <c r="N10" t="n">
-        <v>180.1334963635481</v>
+        <v>180.298816034637</v>
       </c>
       <c r="O10" t="n">
-        <v>13.42138205862377</v>
+        <v>13.42753946315694</v>
       </c>
       <c r="P10" t="n">
-        <v>367.3379514267676</v>
+        <v>367.5724166676135</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21767,28 +21967,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1337428968615103</v>
+        <v>0.1140801608722945</v>
       </c>
       <c r="J11" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006284939836324055</v>
+        <v>0.004664450039307488</v>
       </c>
       <c r="M11" t="n">
-        <v>10.02247888391595</v>
+        <v>9.994651708496134</v>
       </c>
       <c r="N11" t="n">
-        <v>178.9166726252445</v>
+        <v>178.2193608100964</v>
       </c>
       <c r="O11" t="n">
-        <v>13.37597370755656</v>
+        <v>13.3498824268267</v>
       </c>
       <c r="P11" t="n">
-        <v>369.8119908196535</v>
+        <v>369.9918306264597</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21845,28 +22045,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1291994966944453</v>
+        <v>0.1088442503151984</v>
       </c>
       <c r="J12" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K12" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006139938919534349</v>
+        <v>0.00443781134944099</v>
       </c>
       <c r="M12" t="n">
-        <v>9.981842350913508</v>
+        <v>9.966931971848096</v>
       </c>
       <c r="N12" t="n">
-        <v>172.6716070840755</v>
+        <v>172.1549543379454</v>
       </c>
       <c r="O12" t="n">
-        <v>13.14045688262305</v>
+        <v>13.12078329742342</v>
       </c>
       <c r="P12" t="n">
-        <v>371.3357234151955</v>
+        <v>371.5221935211121</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21923,28 +22123,28 @@
         <v>0.0911</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1246579566378893</v>
+        <v>0.1048251881113074</v>
       </c>
       <c r="J13" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K13" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006609512051758748</v>
+        <v>0.004757879335210657</v>
       </c>
       <c r="M13" t="n">
-        <v>9.291018256669558</v>
+        <v>9.273841958839132</v>
       </c>
       <c r="N13" t="n">
-        <v>147.6511118032655</v>
+        <v>147.2942916950482</v>
       </c>
       <c r="O13" t="n">
-        <v>12.15117738341703</v>
+        <v>12.13648596979571</v>
       </c>
       <c r="P13" t="n">
-        <v>370.0917477859531</v>
+        <v>370.2753493798452</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22001,28 +22201,28 @@
         <v>0.0549</v>
       </c>
       <c r="I14" t="n">
-        <v>0.219789335155417</v>
+        <v>0.1940998384292569</v>
       </c>
       <c r="J14" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K14" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0128056769548196</v>
+        <v>0.01017445266258654</v>
       </c>
       <c r="M14" t="n">
-        <v>11.94709798150191</v>
+        <v>11.91663006062236</v>
       </c>
       <c r="N14" t="n">
-        <v>235.1379659154421</v>
+        <v>234.6429054776034</v>
       </c>
       <c r="O14" t="n">
-        <v>15.33420900846999</v>
+        <v>15.31805814970042</v>
       </c>
       <c r="P14" t="n">
-        <v>367.2268374585814</v>
+        <v>367.4644919734961</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22079,28 +22279,28 @@
         <v>0.0408</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3307465231045027</v>
+        <v>0.2854059564253259</v>
       </c>
       <c r="J15" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K15" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01418913023183643</v>
+        <v>0.01078946137550296</v>
       </c>
       <c r="M15" t="n">
-        <v>17.04870961543965</v>
+        <v>16.98817274001467</v>
       </c>
       <c r="N15" t="n">
-        <v>470.1650125012078</v>
+        <v>468.7866199497107</v>
       </c>
       <c r="O15" t="n">
-        <v>21.6832887842506</v>
+        <v>21.65148077960745</v>
       </c>
       <c r="P15" t="n">
-        <v>362.1839144318674</v>
+        <v>362.6077611567736</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22157,28 +22357,28 @@
         <v>0.046</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3685781521672938</v>
+        <v>0.3355428381209709</v>
       </c>
       <c r="J16" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K16" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02000345591710817</v>
+        <v>0.01698759403351846</v>
       </c>
       <c r="M16" t="n">
-        <v>16.2664279054307</v>
+        <v>16.1593557568462</v>
       </c>
       <c r="N16" t="n">
-        <v>425.3209616729197</v>
+        <v>422.0190501157575</v>
       </c>
       <c r="O16" t="n">
-        <v>20.62331112292397</v>
+        <v>20.54310225150422</v>
       </c>
       <c r="P16" t="n">
-        <v>364.1313939624189</v>
+        <v>364.4337944937294</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22235,28 +22435,28 @@
         <v>0.0605</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3866423123988037</v>
+        <v>0.3634333416657336</v>
       </c>
       <c r="J17" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K17" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02986900104399515</v>
+        <v>0.02696272836736191</v>
       </c>
       <c r="M17" t="n">
-        <v>13.40233456790475</v>
+        <v>13.36011444101239</v>
       </c>
       <c r="N17" t="n">
-        <v>310.2891163618872</v>
+        <v>308.7622218960665</v>
       </c>
       <c r="O17" t="n">
-        <v>17.61502530119918</v>
+        <v>17.57163116776774</v>
       </c>
       <c r="P17" t="n">
-        <v>369.4388041836664</v>
+        <v>369.651410927612</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22313,28 +22513,28 @@
         <v>0.0604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4046100781843863</v>
+        <v>0.3792591287207903</v>
       </c>
       <c r="J18" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K18" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04356326950982903</v>
+        <v>0.03905802457795815</v>
       </c>
       <c r="M18" t="n">
-        <v>12.10866629784796</v>
+        <v>12.09965306705834</v>
       </c>
       <c r="N18" t="n">
-        <v>227.2245683782403</v>
+        <v>226.7766143760477</v>
       </c>
       <c r="O18" t="n">
-        <v>15.07396989443194</v>
+        <v>15.05910403629803</v>
       </c>
       <c r="P18" t="n">
-        <v>372.6166780477823</v>
+        <v>372.8513629908672</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22391,28 +22591,28 @@
         <v>0.0539</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2465887917171337</v>
+        <v>0.2252013434198435</v>
       </c>
       <c r="J19" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K19" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01804928520437499</v>
+        <v>0.01535689486749603</v>
       </c>
       <c r="M19" t="n">
-        <v>11.08213785253842</v>
+        <v>11.06331632722207</v>
       </c>
       <c r="N19" t="n">
-        <v>211.4046072760918</v>
+        <v>210.6329790955627</v>
       </c>
       <c r="O19" t="n">
-        <v>14.5397595329528</v>
+        <v>14.51320016728091</v>
       </c>
       <c r="P19" t="n">
-        <v>374.6288888920182</v>
+        <v>374.8248157800494</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -22469,28 +22669,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3974149057952551</v>
+        <v>0.367979239558469</v>
       </c>
       <c r="J20" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K20" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05108118555999031</v>
+        <v>0.04462472929247474</v>
       </c>
       <c r="M20" t="n">
-        <v>10.85611063555949</v>
+        <v>10.8626748369353</v>
       </c>
       <c r="N20" t="n">
-        <v>184.394508554672</v>
+        <v>184.815310927924</v>
       </c>
       <c r="O20" t="n">
-        <v>13.57919395820945</v>
+        <v>13.5946795080989</v>
       </c>
       <c r="P20" t="n">
-        <v>369.3611841275537</v>
+        <v>369.6328636867371</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -22547,28 +22747,28 @@
         <v>0.0654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1432430196658321</v>
+        <v>0.1294593349966283</v>
       </c>
       <c r="J21" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K21" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007744421869071649</v>
+        <v>0.006459067855762002</v>
       </c>
       <c r="M21" t="n">
-        <v>9.935403597051961</v>
+        <v>9.88974377517213</v>
       </c>
       <c r="N21" t="n">
-        <v>171.5007857691248</v>
+        <v>170.4089567003265</v>
       </c>
       <c r="O21" t="n">
-        <v>13.09583085447902</v>
+        <v>13.05407816355971</v>
       </c>
       <c r="P21" t="n">
-        <v>375.659209662376</v>
+        <v>375.7840045834693</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -22625,28 +22825,28 @@
         <v>0.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1990597362466408</v>
+        <v>0.1777795623946287</v>
       </c>
       <c r="J22" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K22" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01514059063589257</v>
+        <v>0.01229304724779123</v>
       </c>
       <c r="M22" t="n">
-        <v>9.970235801471906</v>
+        <v>9.928148255681711</v>
       </c>
       <c r="N22" t="n">
-        <v>167.1757930904079</v>
+        <v>166.8686154409197</v>
       </c>
       <c r="O22" t="n">
-        <v>12.9296478331936</v>
+        <v>12.91776356189103</v>
       </c>
       <c r="P22" t="n">
-        <v>371.952596977674</v>
+        <v>372.146338156206</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -22703,28 +22903,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0006566859375861678</v>
+        <v>-0.01335453741721189</v>
       </c>
       <c r="J23" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K23" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L23" t="n">
-        <v>1.795965166584423e-07</v>
+        <v>7.569745273350303e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>9.291297381025192</v>
+        <v>9.236792082995311</v>
       </c>
       <c r="N23" t="n">
-        <v>154.5600081669296</v>
+        <v>153.6190632622883</v>
       </c>
       <c r="O23" t="n">
-        <v>12.43221654279436</v>
+        <v>12.39431576418353</v>
       </c>
       <c r="P23" t="n">
-        <v>375.090742126646</v>
+        <v>375.2197507657054</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -22781,28 +22981,28 @@
         <v>0.0519</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02075781239173121</v>
+        <v>0.003412670097707856</v>
       </c>
       <c r="J24" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K24" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0002378675589984613</v>
+        <v>6.528803534688876e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>8.462841609117039</v>
+        <v>8.436958040840025</v>
       </c>
       <c r="N24" t="n">
-        <v>116.1597855996679</v>
+        <v>115.9170477213293</v>
       </c>
       <c r="O24" t="n">
-        <v>10.77774492181309</v>
+        <v>10.76647796270114</v>
       </c>
       <c r="P24" t="n">
-        <v>379.8584970996233</v>
+        <v>380.0183149281265</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -22859,28 +23059,28 @@
         <v>0.0529</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.129143210901955</v>
+        <v>-0.1475801592675426</v>
       </c>
       <c r="J25" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K25" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L25" t="n">
-        <v>0.006769935211141886</v>
+        <v>0.008968331022579656</v>
       </c>
       <c r="M25" t="n">
-        <v>10.12852797904706</v>
+        <v>10.08841490299683</v>
       </c>
       <c r="N25" t="n">
-        <v>157.6377080064858</v>
+        <v>157.0636666503152</v>
       </c>
       <c r="O25" t="n">
-        <v>12.55538561759398</v>
+        <v>12.53250440455998</v>
       </c>
       <c r="P25" t="n">
-        <v>392.373194050017</v>
+        <v>392.5433584897611</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -22937,28 +23137,28 @@
         <v>0.042</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.08146496011052437</v>
+        <v>-0.1034687852189649</v>
       </c>
       <c r="J26" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K26" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001793141997944114</v>
+        <v>0.002939376967916352</v>
       </c>
       <c r="M26" t="n">
-        <v>12.5787924016656</v>
+        <v>12.54707152536154</v>
       </c>
       <c r="N26" t="n">
-        <v>232.4920651120133</v>
+        <v>231.5673568563434</v>
       </c>
       <c r="O26" t="n">
-        <v>15.24769048452956</v>
+        <v>15.21733737735822</v>
       </c>
       <c r="P26" t="n">
-        <v>385.4687288749338</v>
+        <v>385.6747962920687</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -23019,28 +23219,28 @@
         <v>0.0332</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01316949755743339</v>
+        <v>-0.00278623752803767</v>
       </c>
       <c r="J27" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K27" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L27" t="n">
-        <v>4.601089142797221e-05</v>
+        <v>2.100942647520476e-06</v>
       </c>
       <c r="M27" t="n">
-        <v>12.61943898356177</v>
+        <v>12.55247938582004</v>
       </c>
       <c r="N27" t="n">
-        <v>242.1534249031184</v>
+        <v>240.5226252633462</v>
       </c>
       <c r="O27" t="n">
-        <v>15.56127966791672</v>
+        <v>15.50879186988291</v>
       </c>
       <c r="P27" t="n">
-        <v>382.224855459126</v>
+        <v>382.371749857919</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -23082,7 +23282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB206"/>
+  <dimension ref="A1:AB208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51828,12 +52028,12 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>-34.71744958635601,173.0781293547906</t>
+          <t>-34.717535752673584,173.0780306858687</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>-34.71789158302187,173.07885686463877</t>
+          <t>-34.71797139371491,173.07876547395753</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -51894,6 +52094,290 @@
       <c r="AB206" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>-34.71047772811296,173.07011781097273</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>-34.711021726379016,173.07072570643962</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>-34.711541522682815,173.0713673104046</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-34.712133909500096,173.07190778922467</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-34.71280740731675,173.07233527350908</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-34.71326314257312,173.07306631892413</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-34.71380385335256,173.07367956850263</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-34.71435008717395,173.07428476845988</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-34.71487551375992,173.0749174969135</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-34.71539925499052,173.07555250679994</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-34.71594827821978,173.07615288518204</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>-34.716493765755715,173.07675688589882</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-34.7170147283,173.07739366643713</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-34.717535752673584,173.0780306858687</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>-34.71801555822295,173.07871490137043</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>-34.71849247728679,173.07940241843326</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>-34.718977562622605,173.08007558401388</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>-34.71944025986797,173.08077028957393</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>-34.71993875575264,173.0814356752461</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>-34.72033504473595,173.08219374908575</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>-34.72079462273789,173.08289218748672</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>-34.72116767472724,173.08366655394843</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>-34.72152244426746,173.08445552451985</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>-34.72184205725405,173.08524994364743</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>-34.72215441571501,173.08603897397637</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>-34.72235015083548,173.08690222625398</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>-34.71051932004048,173.07005987242894</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>-34.71105497640721,173.07067938843352</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>-34.711571341359786,173.071325772447</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-34.712175028658045,173.0718505094495</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-34.71285533047719,173.07226851536691</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-34.71329247082176,173.07302556620363</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-34.713832207659024,173.073640686319</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-34.71437356740119,173.0742529127761</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-34.714906080230996,173.07487602738428</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-34.715429941708024,173.07551087422067</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-34.71597339139452,173.07611957738527</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-34.716518431232096,173.07672683148778</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-34.71705476433567,173.07734782105</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-34.717612483219874,173.0779428215842</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>-34.71804720725646,173.07867866015107</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>-34.718518949882785,173.07937210484113</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>-34.719010323454185,173.08004098762765</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>-34.71947163052515,173.08073998162334</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>-34.719959891945706,173.08141539917392</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>-34.72037377882568,173.08215946639757</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>-34.720828155977806,173.08286609195974</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>-34.72119742647441,173.08364446024717</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>-34.72156042206675,173.084427322339</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>-34.7218770355742,173.08522917082627</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>-34.722196368658324,173.08602148759738</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>-34.72239621506831,173.08688485514236</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0012/nzd0012.xlsx
+++ b/data/nzd0012/nzd0012.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB208"/>
+  <dimension ref="A1:AB209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18759,7 +18759,7 @@
         <v>368.14</v>
       </c>
       <c r="O206" t="n">
-        <v>360.54</v>
+        <v>373.69</v>
       </c>
       <c r="P206" t="n">
         <v>371.45</v>
@@ -18849,7 +18849,7 @@
         <v>362.66</v>
       </c>
       <c r="O207" t="n">
-        <v>360.54</v>
+        <v>373.69</v>
       </c>
       <c r="P207" t="n">
         <v>364.71</v>
@@ -18939,7 +18939,7 @@
         <v>356.55</v>
       </c>
       <c r="O208" t="n">
-        <v>348.83</v>
+        <v>373.69</v>
       </c>
       <c r="P208" t="n">
         <v>359.88</v>
@@ -18980,6 +18980,96 @@
       <c r="AB208" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>346.48</v>
+      </c>
+      <c r="C209" t="n">
+        <v>352.66</v>
+      </c>
+      <c r="D209" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="E209" t="n">
+        <v>348.55</v>
+      </c>
+      <c r="F209" t="n">
+        <v>331.73</v>
+      </c>
+      <c r="G209" t="n">
+        <v>349.85</v>
+      </c>
+      <c r="H209" t="n">
+        <v>353.72</v>
+      </c>
+      <c r="I209" t="n">
+        <v>355</v>
+      </c>
+      <c r="J209" t="n">
+        <v>357.69</v>
+      </c>
+      <c r="K209" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="L209" t="n">
+        <v>362.36</v>
+      </c>
+      <c r="M209" t="n">
+        <v>362.23</v>
+      </c>
+      <c r="N209" t="n">
+        <v>356.55</v>
+      </c>
+      <c r="O209" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="P209" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="R209" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="S209" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="T209" t="n">
+        <v>363.67</v>
+      </c>
+      <c r="U209" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="V209" t="n">
+        <v>363.59</v>
+      </c>
+      <c r="W209" t="n">
+        <v>366.04</v>
+      </c>
+      <c r="X209" t="n">
+        <v>369.25</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>371.73</v>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18994,7 +19084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B210"/>
+  <dimension ref="A1:B211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21097,6 +21187,16 @@
       </c>
       <c r="B210" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -21265,28 +21365,28 @@
         <v>0.0363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09702337233386746</v>
+        <v>0.0830014183232165</v>
       </c>
       <c r="J2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003013868172010326</v>
+        <v>0.002220276311982627</v>
       </c>
       <c r="M2" t="n">
-        <v>10.92691362008363</v>
+        <v>10.94600382571844</v>
       </c>
       <c r="N2" t="n">
-        <v>202.5129309162983</v>
+        <v>202.6505835841611</v>
       </c>
       <c r="O2" t="n">
-        <v>14.23070380959066</v>
+        <v>14.23553945532663</v>
       </c>
       <c r="P2" t="n">
-        <v>359.1927461088764</v>
+        <v>359.3216791056979</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21343,28 +21443,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1124672877655572</v>
+        <v>0.1012898467407615</v>
       </c>
       <c r="J3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005773243231928404</v>
+        <v>0.004717055595329978</v>
       </c>
       <c r="M3" t="n">
-        <v>9.085475176129981</v>
+        <v>9.108932865590868</v>
       </c>
       <c r="N3" t="n">
-        <v>143.1825648681899</v>
+        <v>143.2133582310352</v>
       </c>
       <c r="O3" t="n">
-        <v>11.96589172891807</v>
+        <v>11.96717837382878</v>
       </c>
       <c r="P3" t="n">
-        <v>361.96899083684</v>
+        <v>362.0706858774519</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21421,28 +21521,28 @@
         <v>0.0382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1295519450138916</v>
+        <v>0.1200847549263385</v>
       </c>
       <c r="J4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K4" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009492599199999452</v>
+        <v>0.008222533471665017</v>
       </c>
       <c r="M4" t="n">
-        <v>7.717960379021935</v>
+        <v>7.740192408631675</v>
       </c>
       <c r="N4" t="n">
-        <v>113.8926290754309</v>
+        <v>113.850127582773</v>
       </c>
       <c r="O4" t="n">
-        <v>10.67204896331679</v>
+        <v>10.67005752481086</v>
       </c>
       <c r="P4" t="n">
-        <v>363.4912751073726</v>
+        <v>363.5783266829618</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21499,28 +21599,28 @@
         <v>0.0403</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1339411042322107</v>
+        <v>0.1224560242924566</v>
       </c>
       <c r="J5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K5" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005942437373034681</v>
+        <v>0.005009071643712781</v>
       </c>
       <c r="M5" t="n">
-        <v>10.32966665679805</v>
+        <v>10.3369625403819</v>
       </c>
       <c r="N5" t="n">
-        <v>195.1685487756023</v>
+        <v>194.9716069959308</v>
       </c>
       <c r="O5" t="n">
-        <v>13.97027375449752</v>
+        <v>13.96322337413288</v>
       </c>
       <c r="P5" t="n">
-        <v>357.4974115771424</v>
+        <v>357.6030178124959</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21577,28 +21677,28 @@
         <v>0.0402</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2146278549109991</v>
+        <v>0.1878714370782716</v>
       </c>
       <c r="J6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K6" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01139840901326061</v>
+        <v>0.008723975969089692</v>
       </c>
       <c r="M6" t="n">
-        <v>12.14745722309795</v>
+        <v>12.21373696641238</v>
       </c>
       <c r="N6" t="n">
-        <v>258.2294558882888</v>
+        <v>260.9541807986687</v>
       </c>
       <c r="O6" t="n">
-        <v>16.06951946662652</v>
+        <v>16.15407629048064</v>
       </c>
       <c r="P6" t="n">
-        <v>354.7396474436281</v>
+        <v>354.9856224387186</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21655,28 +21755,28 @@
         <v>0.0688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1102281625474089</v>
+        <v>0.09996743632100014</v>
       </c>
       <c r="J7" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K7" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003641658311364315</v>
+        <v>0.003022898465247281</v>
       </c>
       <c r="M7" t="n">
-        <v>11.14713414578971</v>
+        <v>11.14394601691157</v>
       </c>
       <c r="N7" t="n">
-        <v>216.190529470897</v>
+        <v>215.7386295724692</v>
       </c>
       <c r="O7" t="n">
-        <v>14.70341897216076</v>
+        <v>14.68804376261417</v>
       </c>
       <c r="P7" t="n">
-        <v>358.1043079910525</v>
+        <v>358.1986561953705</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21733,28 +21833,28 @@
         <v>0.0762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1028260599335324</v>
+        <v>0.09382530963163442</v>
       </c>
       <c r="J8" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K8" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003797151410229405</v>
+        <v>0.003191337829072438</v>
       </c>
       <c r="M8" t="n">
-        <v>10.3183616433244</v>
+        <v>10.31248860156281</v>
       </c>
       <c r="N8" t="n">
-        <v>180.3978747177241</v>
+        <v>179.981645640803</v>
       </c>
       <c r="O8" t="n">
-        <v>13.43122759533633</v>
+        <v>13.41572382097973</v>
       </c>
       <c r="P8" t="n">
-        <v>360.7900223322084</v>
+        <v>360.8727849563894</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21811,28 +21911,28 @@
         <v>0.0827</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1316129192168671</v>
+        <v>0.1206382126455537</v>
       </c>
       <c r="J9" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K9" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005273765716647616</v>
+        <v>0.004471252259434677</v>
       </c>
       <c r="M9" t="n">
-        <v>10.8070879108487</v>
+        <v>10.7965798622986</v>
       </c>
       <c r="N9" t="n">
-        <v>212.6765824507026</v>
+        <v>212.3175508948644</v>
       </c>
       <c r="O9" t="n">
-        <v>14.58343520747779</v>
+        <v>14.57112044061349</v>
       </c>
       <c r="P9" t="n">
-        <v>363.3736650165815</v>
+        <v>363.4742995702198</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21889,28 +21989,28 @@
         <v>0.0687</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1736503542364086</v>
+        <v>0.1603843632705509</v>
       </c>
       <c r="J10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K10" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01083103184422407</v>
+        <v>0.009307637247484402</v>
       </c>
       <c r="M10" t="n">
-        <v>10.10053526731317</v>
+        <v>10.10426225875503</v>
       </c>
       <c r="N10" t="n">
-        <v>180.298816034637</v>
+        <v>180.4324943476915</v>
       </c>
       <c r="O10" t="n">
-        <v>13.42753946315694</v>
+        <v>13.43251630736741</v>
       </c>
       <c r="P10" t="n">
-        <v>367.5724166676135</v>
+        <v>367.6931333480196</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21967,28 +22067,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1140801608722945</v>
+        <v>0.1026454321579495</v>
       </c>
       <c r="J11" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004664450039307488</v>
+        <v>0.003809593224005092</v>
       </c>
       <c r="M11" t="n">
-        <v>9.994651708496134</v>
+        <v>9.986388975805008</v>
       </c>
       <c r="N11" t="n">
-        <v>178.2193608100964</v>
+        <v>178.0469351234804</v>
       </c>
       <c r="O11" t="n">
-        <v>13.3498824268267</v>
+        <v>13.34342291630901</v>
       </c>
       <c r="P11" t="n">
-        <v>369.9918306264597</v>
+        <v>370.0968041526095</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22045,28 +22145,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1088442503151984</v>
+        <v>0.09771266077945609</v>
       </c>
       <c r="J12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K12" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00443781134944099</v>
+        <v>0.003606085751189481</v>
       </c>
       <c r="M12" t="n">
-        <v>9.966931971848096</v>
+        <v>9.963103533144524</v>
       </c>
       <c r="N12" t="n">
-        <v>172.1549543379454</v>
+        <v>172.0150912098286</v>
       </c>
       <c r="O12" t="n">
-        <v>13.12078329742342</v>
+        <v>13.11545238296524</v>
       </c>
       <c r="P12" t="n">
-        <v>371.5221935211121</v>
+        <v>371.6245629567712</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22123,28 +22223,28 @@
         <v>0.0911</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1048251881113074</v>
+        <v>0.09471672113129027</v>
       </c>
       <c r="J13" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K13" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004757879335210657</v>
+        <v>0.003917653453711201</v>
       </c>
       <c r="M13" t="n">
-        <v>9.273841958839132</v>
+        <v>9.266517580572391</v>
       </c>
       <c r="N13" t="n">
-        <v>147.2942916950482</v>
+        <v>147.1408589078767</v>
       </c>
       <c r="O13" t="n">
-        <v>12.13648596979571</v>
+        <v>12.13016318554193</v>
       </c>
       <c r="P13" t="n">
-        <v>370.2753493798452</v>
+        <v>370.3692880694662</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22201,28 +22301,28 @@
         <v>0.0549</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1940998384292569</v>
+        <v>0.1789105968164776</v>
       </c>
       <c r="J14" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K14" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01017445266258654</v>
+        <v>0.008711748611921033</v>
       </c>
       <c r="M14" t="n">
-        <v>11.91663006062236</v>
+        <v>11.91059322414437</v>
       </c>
       <c r="N14" t="n">
-        <v>234.6429054776034</v>
+        <v>234.7458608461534</v>
       </c>
       <c r="O14" t="n">
-        <v>15.31805814970042</v>
+        <v>15.32141836926834</v>
       </c>
       <c r="P14" t="n">
-        <v>367.4644919734961</v>
+        <v>367.60554028979</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22279,28 +22379,28 @@
         <v>0.0408</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2854059564253259</v>
+        <v>0.3416692247270585</v>
       </c>
       <c r="J15" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K15" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01078946137550296</v>
+        <v>0.01568019079267691</v>
       </c>
       <c r="M15" t="n">
-        <v>16.98817274001467</v>
+        <v>16.86388305257673</v>
       </c>
       <c r="N15" t="n">
-        <v>468.7866199497107</v>
+        <v>463.2750642903204</v>
       </c>
       <c r="O15" t="n">
-        <v>21.65148077960745</v>
+        <v>21.52382550315627</v>
       </c>
       <c r="P15" t="n">
-        <v>362.6077611567736</v>
+        <v>362.0815711237053</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22357,28 +22457,28 @@
         <v>0.046</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3355428381209709</v>
+        <v>0.3230539997160504</v>
       </c>
       <c r="J16" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K16" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01698759403351846</v>
+        <v>0.01591238891249802</v>
       </c>
       <c r="M16" t="n">
-        <v>16.1593557568462</v>
+        <v>16.13731998194366</v>
       </c>
       <c r="N16" t="n">
-        <v>422.0190501157575</v>
+        <v>420.8414215023905</v>
       </c>
       <c r="O16" t="n">
-        <v>20.54310225150422</v>
+        <v>20.51441984318324</v>
       </c>
       <c r="P16" t="n">
-        <v>364.4337944937294</v>
+        <v>364.5486455970191</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22435,28 +22535,28 @@
         <v>0.0605</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3634333416657336</v>
+        <v>0.3519627049906653</v>
       </c>
       <c r="J17" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K17" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02696272836736191</v>
+        <v>0.02555470818673555</v>
       </c>
       <c r="M17" t="n">
-        <v>13.36011444101239</v>
+        <v>13.33890757862938</v>
       </c>
       <c r="N17" t="n">
-        <v>308.7622218960665</v>
+        <v>307.9992674648983</v>
       </c>
       <c r="O17" t="n">
-        <v>17.57163116776774</v>
+        <v>17.54990790474122</v>
       </c>
       <c r="P17" t="n">
-        <v>369.651410927612</v>
+        <v>369.7568983424423</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22513,28 +22613,28 @@
         <v>0.0604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3792591287207903</v>
+        <v>0.365337131706603</v>
       </c>
       <c r="J18" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K18" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03905802457795815</v>
+        <v>0.03658287871580423</v>
       </c>
       <c r="M18" t="n">
-        <v>12.09965306705834</v>
+        <v>12.10255523417991</v>
       </c>
       <c r="N18" t="n">
-        <v>226.7766143760477</v>
+        <v>226.7435082589127</v>
       </c>
       <c r="O18" t="n">
-        <v>15.05910403629803</v>
+        <v>15.05800479010791</v>
       </c>
       <c r="P18" t="n">
-        <v>372.8513629908672</v>
+        <v>372.9807410814328</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22591,28 +22691,28 @@
         <v>0.0539</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2252013434198435</v>
+        <v>0.2127421180147621</v>
       </c>
       <c r="J19" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K19" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01535689486749603</v>
+        <v>0.01382657037177359</v>
       </c>
       <c r="M19" t="n">
-        <v>11.06331632722207</v>
+        <v>11.06106869376203</v>
       </c>
       <c r="N19" t="n">
-        <v>210.6329790955627</v>
+        <v>210.4823290181203</v>
       </c>
       <c r="O19" t="n">
-        <v>14.51320016728091</v>
+        <v>14.50800913351381</v>
       </c>
       <c r="P19" t="n">
-        <v>374.8248157800494</v>
+        <v>374.939394553312</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -22669,28 +22769,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.367979239558469</v>
+        <v>0.3528408484012832</v>
       </c>
       <c r="J20" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K20" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04462472929247474</v>
+        <v>0.04138625536687768</v>
       </c>
       <c r="M20" t="n">
-        <v>10.8626748369353</v>
+        <v>10.86927359155235</v>
       </c>
       <c r="N20" t="n">
-        <v>184.815310927924</v>
+        <v>185.1210586322733</v>
       </c>
       <c r="O20" t="n">
-        <v>13.5946795080989</v>
+        <v>13.60591998478138</v>
       </c>
       <c r="P20" t="n">
-        <v>369.6328636867371</v>
+        <v>369.7731247331418</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -22747,28 +22847,28 @@
         <v>0.0654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1294593349966283</v>
+        <v>0.1191076077042461</v>
       </c>
       <c r="J21" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K21" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L21" t="n">
-        <v>0.006459067855762002</v>
+        <v>0.005514848938353412</v>
       </c>
       <c r="M21" t="n">
-        <v>9.88974377517213</v>
+        <v>9.881582861828027</v>
       </c>
       <c r="N21" t="n">
-        <v>170.4089567003265</v>
+        <v>170.1934363375286</v>
       </c>
       <c r="O21" t="n">
-        <v>13.05407816355971</v>
+        <v>13.04582064638053</v>
       </c>
       <c r="P21" t="n">
-        <v>375.7840045834693</v>
+        <v>375.8780857094847</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -22825,28 +22925,28 @@
         <v>0.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1777795623946287</v>
+        <v>0.1657016830974001</v>
       </c>
       <c r="J22" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K22" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01229304724779123</v>
+        <v>0.01076179945245426</v>
       </c>
       <c r="M22" t="n">
-        <v>9.928148255681711</v>
+        <v>9.913541728983622</v>
       </c>
       <c r="N22" t="n">
-        <v>166.8686154409197</v>
+        <v>166.9071905693128</v>
       </c>
       <c r="O22" t="n">
-        <v>12.91776356189103</v>
+        <v>12.91925657959129</v>
       </c>
       <c r="P22" t="n">
-        <v>372.146338156206</v>
+        <v>372.256736250311</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -22903,28 +23003,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.01335453741721189</v>
+        <v>-0.02141515765177654</v>
       </c>
       <c r="J23" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K23" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L23" t="n">
-        <v>7.569745273350303e-05</v>
+        <v>0.0001963492126373367</v>
       </c>
       <c r="M23" t="n">
-        <v>9.236792082995311</v>
+        <v>9.214012620597588</v>
       </c>
       <c r="N23" t="n">
-        <v>153.6190632622883</v>
+        <v>153.2392427711805</v>
       </c>
       <c r="O23" t="n">
-        <v>12.39431576418353</v>
+        <v>12.37898391513538</v>
       </c>
       <c r="P23" t="n">
-        <v>375.2197507657054</v>
+        <v>375.2942589770048</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -22981,28 +23081,28 @@
         <v>0.0519</v>
       </c>
       <c r="I24" t="n">
-        <v>0.003412670097707856</v>
+        <v>-0.006521546930720858</v>
       </c>
       <c r="J24" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K24" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L24" t="n">
-        <v>6.528803534688876e-06</v>
+        <v>2.399360466487366e-05</v>
       </c>
       <c r="M24" t="n">
-        <v>8.436958040840025</v>
+        <v>8.428367540804732</v>
       </c>
       <c r="N24" t="n">
-        <v>115.9170477213293</v>
+        <v>115.9181835074268</v>
       </c>
       <c r="O24" t="n">
-        <v>10.76647796270114</v>
+        <v>10.76653070898081</v>
       </c>
       <c r="P24" t="n">
-        <v>380.0183149281265</v>
+        <v>380.1102026275229</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -23059,28 +23159,28 @@
         <v>0.0529</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1475801592675426</v>
+        <v>-0.159328981692308</v>
       </c>
       <c r="J25" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K25" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L25" t="n">
-        <v>0.008968331022579656</v>
+        <v>0.0105013646518668</v>
       </c>
       <c r="M25" t="n">
-        <v>10.08841490299683</v>
+        <v>10.07660875072497</v>
       </c>
       <c r="N25" t="n">
-        <v>157.0636666503152</v>
+        <v>157.0825973783191</v>
       </c>
       <c r="O25" t="n">
-        <v>12.53250440455998</v>
+        <v>12.53325964696811</v>
       </c>
       <c r="P25" t="n">
-        <v>392.5433584897611</v>
+        <v>392.65222516311</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -23137,28 +23237,28 @@
         <v>0.042</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1034687852189649</v>
+        <v>-0.1170575962582673</v>
       </c>
       <c r="J26" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K26" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L26" t="n">
-        <v>0.002939376967916352</v>
+        <v>0.003784923643020854</v>
       </c>
       <c r="M26" t="n">
-        <v>12.54707152536154</v>
+        <v>12.54247401415544</v>
       </c>
       <c r="N26" t="n">
-        <v>231.5673568563434</v>
+        <v>231.4628889905244</v>
       </c>
       <c r="O26" t="n">
-        <v>15.21733737735822</v>
+        <v>15.21390446238323</v>
       </c>
       <c r="P26" t="n">
-        <v>385.6747962920687</v>
+        <v>385.8025457708962</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -23219,28 +23319,28 @@
         <v>0.0332</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.00278623752803767</v>
+        <v>-0.01252343633469908</v>
       </c>
       <c r="J27" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K27" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L27" t="n">
-        <v>2.100942647520476e-06</v>
+        <v>4.283072825916889e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>12.55247938582004</v>
+        <v>12.52588223110852</v>
       </c>
       <c r="N27" t="n">
-        <v>240.5226252633462</v>
+        <v>239.8755831073548</v>
       </c>
       <c r="O27" t="n">
-        <v>15.50879186988291</v>
+        <v>15.48791732633393</v>
       </c>
       <c r="P27" t="n">
-        <v>382.371749857919</v>
+        <v>382.4617371735492</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -23282,7 +23382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB208"/>
+  <dimension ref="A1:AB209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52028,7 +52128,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>-34.717535752673584,173.0780306858687</t>
+          <t>-34.71744958635601,173.0781293547906</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -52170,7 +52270,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>-34.717535752673584,173.0780306858687</t>
+          <t>-34.71744958635601,173.0781293547906</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -52312,7 +52412,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>-34.717612483219874,173.0779428215842</t>
+          <t>-34.71744958635601,173.0781293547906</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -52378,6 +52478,148 @@
       <c r="AB208" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-34.71051932004048,173.07005987242894</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>-34.71103988965284,173.07070040461525</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>-34.711573589592795,173.07132264061565</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-34.71217846018367,173.07184572926423</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-34.712835096258395,173.07229670214744</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-34.713285123948644,173.07303577496862</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-34.7138185379002,173.0736594316277</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-34.714361917366226,173.07426871841173</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-34.714896471911565,173.07488906299596</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-34.7154274195126,173.07551429607767</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-34.715969925412125,173.07612417434632</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-34.71651016702692,173.07673690126666</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-34.71705476433567,173.07734782105</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-34.71742855258864,173.07815344048115</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>-34.71804720725646,173.07867866015107</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>-34.71850800700369,173.079384635462</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>-34.71900672112257,173.08004479179596</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>-34.719472758458735,173.08073889189885</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>-34.71995692298235,173.08141824731845</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>-34.72038426323924,173.08215018686744</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>-34.72082694210496,173.08286703659456</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>-34.72119389009124,173.08364708637268</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>-34.72155504059762,173.08443131860102</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>-34.72188529434369,173.0852242661298</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>-34.72220336081527,173.0860185731992</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>-34.72239277101361,173.08688615391773</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
